--- a/IV_3.5K_T2.xlsx
+++ b/IV_3.5K_T2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2374,7 +2374,7 @@
         <v>29.6875</v>
       </c>
       <c r="AD24">
-        <v>5.1959999999999999E-2</v>
+        <v>5.1990000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -2466,7 +2466,7 @@
         <v>31.25</v>
       </c>
       <c r="AD25">
-        <v>5.4699999999999999E-2</v>
+        <v>5.4679999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -2558,7 +2558,7 @@
         <v>32.8125</v>
       </c>
       <c r="AD26">
-        <v>5.7430000000000002E-2</v>
+        <v>5.7419999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -2730,7 +2730,7 @@
         <v>35.9375</v>
       </c>
       <c r="Z28">
-        <v>6.2969999999999998E-2</v>
+        <v>6.2990000000000004E-2</v>
       </c>
       <c r="AA28">
         <v>35.9375</v>
@@ -2742,7 +2742,7 @@
         <v>35.9375</v>
       </c>
       <c r="AD28">
-        <v>6.2899999999999998E-2</v>
+        <v>6.3100000000000003E-2</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -2834,7 +2834,7 @@
         <v>37.5</v>
       </c>
       <c r="AD29">
-        <v>6.5659999999999996E-2</v>
+        <v>6.565E-2</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -2908,7 +2908,7 @@
         <v>39.0625</v>
       </c>
       <c r="X30">
-        <v>6.8430000000000005E-2</v>
+        <v>6.8449999999999997E-2</v>
       </c>
       <c r="Y30">
         <v>39.0625</v>
@@ -3006,7 +3006,7 @@
         <v>40.625</v>
       </c>
       <c r="Z31">
-        <v>7.1190000000000003E-2</v>
+        <v>7.1249999999999994E-2</v>
       </c>
       <c r="AA31">
         <v>40.625</v>
@@ -3018,7 +3018,7 @@
         <v>40.625</v>
       </c>
       <c r="AD31">
-        <v>7.1129999999999999E-2</v>
+        <v>7.1150000000000005E-2</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -3086,7 +3086,7 @@
         <v>42.1875</v>
       </c>
       <c r="V32">
-        <v>7.3929999999999996E-2</v>
+        <v>7.3980000000000004E-2</v>
       </c>
       <c r="W32">
         <v>42.1875</v>
@@ -3098,7 +3098,7 @@
         <v>42.1875</v>
       </c>
       <c r="Z32">
-        <v>7.3950000000000002E-2</v>
+        <v>7.3980000000000004E-2</v>
       </c>
       <c r="AA32">
         <v>42.1875</v>
@@ -3110,7 +3110,7 @@
         <v>42.1875</v>
       </c>
       <c r="AD32">
-        <v>7.3880000000000001E-2</v>
+        <v>7.3889999999999997E-2</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -3190,7 +3190,7 @@
         <v>43.75</v>
       </c>
       <c r="Z33">
-        <v>7.6679999999999998E-2</v>
+        <v>7.671E-2</v>
       </c>
       <c r="AA33">
         <v>43.75</v>
@@ -3270,7 +3270,7 @@
         <v>45.3125</v>
       </c>
       <c r="V34">
-        <v>7.9420000000000004E-2</v>
+        <v>7.9399999999999998E-2</v>
       </c>
       <c r="W34">
         <v>45.3125</v>
@@ -3294,7 +3294,7 @@
         <v>45.3125</v>
       </c>
       <c r="AD34">
-        <v>7.9350000000000004E-2</v>
+        <v>7.9409999999999994E-2</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -3356,7 +3356,7 @@
         <v>46.875</v>
       </c>
       <c r="T35">
-        <v>8.2150000000000001E-2</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="U35">
         <v>46.875</v>
@@ -3374,7 +3374,7 @@
         <v>46.875</v>
       </c>
       <c r="Z35">
-        <v>8.2150000000000001E-2</v>
+        <v>8.2110000000000002E-2</v>
       </c>
       <c r="AA35">
         <v>46.875</v>
@@ -3386,7 +3386,7 @@
         <v>46.875</v>
       </c>
       <c r="AD35">
-        <v>8.2110000000000002E-2</v>
+        <v>8.2119999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -3454,7 +3454,7 @@
         <v>48.4375</v>
       </c>
       <c r="V36">
-        <v>8.4909999999999999E-2</v>
+        <v>8.4919999999999995E-2</v>
       </c>
       <c r="W36">
         <v>48.4375</v>
@@ -3478,7 +3478,7 @@
         <v>48.4375</v>
       </c>
       <c r="AD36">
-        <v>8.4820000000000007E-2</v>
+        <v>8.4830000000000003E-2</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <v>50</v>
       </c>
       <c r="R37">
-        <v>8.7749999999999995E-2</v>
+        <v>8.7770000000000001E-2</v>
       </c>
       <c r="S37">
         <v>50</v>
@@ -3546,7 +3546,7 @@
         <v>50</v>
       </c>
       <c r="V37">
-        <v>8.7730000000000002E-2</v>
+        <v>8.7709999999999996E-2</v>
       </c>
       <c r="W37">
         <v>50</v>
@@ -3626,7 +3626,7 @@
         <v>51.5625</v>
       </c>
       <c r="R38">
-        <v>9.0459999999999999E-2</v>
+        <v>9.0450000000000003E-2</v>
       </c>
       <c r="S38">
         <v>51.5625</v>
@@ -3638,7 +3638,7 @@
         <v>51.5625</v>
       </c>
       <c r="V38">
-        <v>9.0459999999999999E-2</v>
+        <v>9.042E-2</v>
       </c>
       <c r="W38">
         <v>51.5625</v>
@@ -3650,7 +3650,7 @@
         <v>51.5625</v>
       </c>
       <c r="Z38">
-        <v>9.0459999999999999E-2</v>
+        <v>9.0509999999999993E-2</v>
       </c>
       <c r="AA38">
         <v>51.5625</v>
@@ -3662,7 +3662,7 @@
         <v>51.5625</v>
       </c>
       <c r="AD38">
-        <v>9.0399999999999994E-2</v>
+        <v>9.0319999999999998E-2</v>
       </c>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
@@ -3712,7 +3712,7 @@
         <v>53.125</v>
       </c>
       <c r="P39">
-        <v>9.3240000000000003E-2</v>
+        <v>9.325E-2</v>
       </c>
       <c r="Q39">
         <v>53.125</v>
@@ -3730,7 +3730,7 @@
         <v>53.125</v>
       </c>
       <c r="V39">
-        <v>9.3200000000000005E-2</v>
+        <v>9.3219999999999997E-2</v>
       </c>
       <c r="W39">
         <v>53.125</v>
@@ -3754,7 +3754,7 @@
         <v>53.125</v>
       </c>
       <c r="AD39">
-        <v>9.3130000000000004E-2</v>
+        <v>9.3179999999999999E-2</v>
       </c>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>54.6875</v>
       </c>
       <c r="R40">
-        <v>9.5960000000000004E-2</v>
+        <v>9.5909999999999995E-2</v>
       </c>
       <c r="S40">
         <v>54.6875</v>
@@ -3822,7 +3822,7 @@
         <v>54.6875</v>
       </c>
       <c r="V40">
-        <v>9.5960000000000004E-2</v>
+        <v>9.5990000000000006E-2</v>
       </c>
       <c r="W40">
         <v>54.6875</v>
@@ -3846,7 +3846,7 @@
         <v>54.6875</v>
       </c>
       <c r="AD40">
-        <v>9.5869999999999997E-2</v>
+        <v>9.5880000000000007E-2</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
@@ -3902,7 +3902,7 @@
         <v>56.25</v>
       </c>
       <c r="R41">
-        <v>9.8710000000000006E-2</v>
+        <v>9.8720000000000002E-2</v>
       </c>
       <c r="S41">
         <v>56.25</v>
@@ -3994,7 +3994,7 @@
         <v>57.8125</v>
       </c>
       <c r="R42">
-        <v>0.10145</v>
+        <v>0.10147</v>
       </c>
       <c r="S42">
         <v>57.8125</v>
@@ -4006,19 +4006,19 @@
         <v>57.8125</v>
       </c>
       <c r="V42">
-        <v>0.10142</v>
+        <v>0.10144</v>
       </c>
       <c r="W42">
         <v>57.8125</v>
       </c>
       <c r="X42">
-        <v>0.10134</v>
+        <v>0.10131999999999999</v>
       </c>
       <c r="Y42">
         <v>57.8125</v>
       </c>
       <c r="Z42">
-        <v>0.10134</v>
+        <v>0.10131999999999999</v>
       </c>
       <c r="AA42">
         <v>57.8125</v>
@@ -4068,7 +4068,7 @@
         <v>59.375</v>
       </c>
       <c r="L43">
-        <v>0.10407</v>
+        <v>0.10408000000000001</v>
       </c>
       <c r="M43">
         <v>59.375</v>
@@ -4086,7 +4086,7 @@
         <v>59.375</v>
       </c>
       <c r="R43">
-        <v>0.1042</v>
+        <v>0.10412</v>
       </c>
       <c r="S43">
         <v>59.375</v>
@@ -4098,7 +4098,7 @@
         <v>59.375</v>
       </c>
       <c r="V43">
-        <v>0.10417999999999999</v>
+        <v>0.10412</v>
       </c>
       <c r="W43">
         <v>59.375</v>
@@ -4110,7 +4110,7 @@
         <v>59.375</v>
       </c>
       <c r="Z43">
-        <v>0.10412</v>
+        <v>0.10410999999999999</v>
       </c>
       <c r="AA43">
         <v>59.375</v>
@@ -4148,7 +4148,7 @@
         <v>60.9375</v>
       </c>
       <c r="H44">
-        <v>0.1069</v>
+        <v>0.1071</v>
       </c>
       <c r="I44">
         <v>60.9375</v>
@@ -4166,7 +4166,7 @@
         <v>60.9375</v>
       </c>
       <c r="N44">
-        <v>0.10685</v>
+        <v>0.10687000000000001</v>
       </c>
       <c r="O44">
         <v>60.9375</v>
@@ -4190,13 +4190,13 @@
         <v>60.9375</v>
       </c>
       <c r="V44">
-        <v>0.10692</v>
+        <v>0.10698000000000001</v>
       </c>
       <c r="W44">
         <v>60.9375</v>
       </c>
       <c r="X44">
-        <v>0.10681</v>
+        <v>0.10680000000000001</v>
       </c>
       <c r="Y44">
         <v>60.9375</v>
@@ -4246,7 +4246,7 @@
         <v>62.5</v>
       </c>
       <c r="J45">
-        <v>0.10893</v>
+        <v>0.10897999999999999</v>
       </c>
       <c r="K45">
         <v>62.5</v>
@@ -4270,7 +4270,7 @@
         <v>62.5</v>
       </c>
       <c r="R45">
-        <v>0.10969</v>
+        <v>0.10971</v>
       </c>
       <c r="S45">
         <v>62.5</v>
@@ -4288,13 +4288,13 @@
         <v>62.5</v>
       </c>
       <c r="X45">
-        <v>0.10959000000000001</v>
+        <v>0.10961</v>
       </c>
       <c r="Y45">
         <v>62.5</v>
       </c>
       <c r="Z45">
-        <v>0.10961</v>
+        <v>0.10962</v>
       </c>
       <c r="AA45">
         <v>62.5</v>
@@ -4374,19 +4374,19 @@
         <v>64.0625</v>
       </c>
       <c r="V46">
-        <v>0.11241</v>
+        <v>0.11244</v>
       </c>
       <c r="W46">
         <v>64.0625</v>
       </c>
       <c r="X46">
-        <v>0.11232</v>
+        <v>0.11230999999999999</v>
       </c>
       <c r="Y46">
         <v>64.0625</v>
       </c>
       <c r="Z46">
-        <v>0.11234</v>
+        <v>0.11232</v>
       </c>
       <c r="AA46">
         <v>64.0625</v>
@@ -4454,7 +4454,7 @@
         <v>65.625</v>
       </c>
       <c r="R47">
-        <v>0.11516</v>
+        <v>0.11516999999999999</v>
       </c>
       <c r="S47">
         <v>65.625</v>
@@ -4466,13 +4466,13 @@
         <v>65.625</v>
       </c>
       <c r="V47">
-        <v>0.11516</v>
+        <v>0.11515</v>
       </c>
       <c r="W47">
         <v>65.625</v>
       </c>
       <c r="X47">
-        <v>0.11506</v>
+        <v>0.11509999999999999</v>
       </c>
       <c r="Y47">
         <v>65.625</v>
@@ -4498,7 +4498,7 @@
         <v>67.1875</v>
       </c>
       <c r="B48">
-        <v>0.11758</v>
+        <v>0.11731</v>
       </c>
       <c r="C48" s="1">
         <v>67.1875</v>
@@ -4546,7 +4546,7 @@
         <v>67.1875</v>
       </c>
       <c r="R48">
-        <v>0.11792</v>
+        <v>0.11797000000000001</v>
       </c>
       <c r="S48">
         <v>67.1875</v>
@@ -4558,19 +4558,19 @@
         <v>67.1875</v>
       </c>
       <c r="V48">
-        <v>0.1179</v>
+        <v>0.1181</v>
       </c>
       <c r="W48">
         <v>67.1875</v>
       </c>
       <c r="X48">
-        <v>0.11781</v>
+        <v>0.11781999999999999</v>
       </c>
       <c r="Y48">
         <v>67.1875</v>
       </c>
       <c r="Z48">
-        <v>0.11783</v>
+        <v>0.11785</v>
       </c>
       <c r="AA48">
         <v>67.1875</v>
@@ -4590,7 +4590,7 @@
         <v>68.75</v>
       </c>
       <c r="B49">
-        <v>0.12031</v>
+        <v>0.12028</v>
       </c>
       <c r="C49" s="1">
         <v>68.75</v>
@@ -4614,7 +4614,7 @@
         <v>68.75</v>
       </c>
       <c r="J49">
-        <v>0.12009</v>
+        <v>0.12010999999999999</v>
       </c>
       <c r="K49">
         <v>68.75</v>
@@ -4656,7 +4656,7 @@
         <v>68.75</v>
       </c>
       <c r="X49">
-        <v>0.12055</v>
+        <v>0.12052</v>
       </c>
       <c r="Y49">
         <v>68.75</v>
@@ -4682,7 +4682,7 @@
         <v>70.3125</v>
       </c>
       <c r="B50">
-        <v>0.12307</v>
+        <v>0.12324</v>
       </c>
       <c r="C50" s="1">
         <v>70.3125</v>
@@ -4706,7 +4706,7 @@
         <v>70.3125</v>
       </c>
       <c r="J50">
-        <v>0.12314</v>
+        <v>0.12316000000000001</v>
       </c>
       <c r="K50">
         <v>70.3125</v>
@@ -4730,7 +4730,7 @@
         <v>70.3125</v>
       </c>
       <c r="R50">
-        <v>0.12339</v>
+        <v>0.12338</v>
       </c>
       <c r="S50">
         <v>70.3125</v>
@@ -4754,7 +4754,7 @@
         <v>70.3125</v>
       </c>
       <c r="Z50">
-        <v>0.12330000000000001</v>
+        <v>0.1235</v>
       </c>
       <c r="AA50">
         <v>70.3125</v>
@@ -4774,7 +4774,7 @@
         <v>71.875</v>
       </c>
       <c r="B51">
-        <v>0.1258</v>
+        <v>0.12609999999999999</v>
       </c>
       <c r="C51" s="1">
         <v>71.875</v>
@@ -4798,7 +4798,7 @@
         <v>71.875</v>
       </c>
       <c r="J51">
-        <v>0.12617999999999999</v>
+        <v>0.12620000000000001</v>
       </c>
       <c r="K51">
         <v>71.875</v>
@@ -4840,13 +4840,13 @@
         <v>71.875</v>
       </c>
       <c r="X51">
-        <v>0.12604000000000001</v>
+        <v>0.12608</v>
       </c>
       <c r="Y51">
         <v>71.875</v>
       </c>
       <c r="Z51">
-        <v>0.12606000000000001</v>
+        <v>0.12605</v>
       </c>
       <c r="AA51">
         <v>71.875</v>
@@ -4866,7 +4866,7 @@
         <v>73.4375</v>
       </c>
       <c r="B52">
-        <v>0.12856000000000001</v>
+        <v>0.12884000000000001</v>
       </c>
       <c r="C52" s="1">
         <v>73.4375</v>
@@ -4932,13 +4932,13 @@
         <v>73.4375</v>
       </c>
       <c r="X52">
-        <v>0.12877</v>
+        <v>0.12878000000000001</v>
       </c>
       <c r="Y52">
         <v>73.4375</v>
       </c>
       <c r="Z52">
-        <v>0.12881999999999999</v>
+        <v>0.12884999999999999</v>
       </c>
       <c r="AA52">
         <v>73.4375</v>
@@ -4958,7 +4958,7 @@
         <v>75</v>
       </c>
       <c r="B53">
-        <v>0.13128999999999999</v>
+        <v>0.13156999999999999</v>
       </c>
       <c r="C53">
         <v>75</v>
@@ -4982,7 +4982,7 @@
         <v>75</v>
       </c>
       <c r="J53">
-        <v>0.13125000000000001</v>
+        <v>0.13127</v>
       </c>
       <c r="K53">
         <v>75</v>
@@ -5024,7 +5024,7 @@
         <v>75</v>
       </c>
       <c r="X53">
-        <v>0.13150999999999999</v>
+        <v>0.13152</v>
       </c>
       <c r="Y53">
         <v>75</v>
@@ -5050,7 +5050,7 @@
         <v>76.5625</v>
       </c>
       <c r="B54">
-        <v>0.13403000000000001</v>
+        <v>0.13433</v>
       </c>
       <c r="C54">
         <v>76.5625</v>
@@ -5116,13 +5116,13 @@
         <v>76.5625</v>
       </c>
       <c r="X54">
-        <v>0.13424</v>
+        <v>0.13422000000000001</v>
       </c>
       <c r="Y54">
         <v>76.5625</v>
       </c>
       <c r="Z54">
-        <v>0.13428999999999999</v>
+        <v>0.13431000000000001</v>
       </c>
       <c r="AA54">
         <v>76.5625</v>
@@ -5142,7 +5142,7 @@
         <v>78.125</v>
       </c>
       <c r="B55">
-        <v>0.13678000000000001</v>
+        <v>0.13708000000000001</v>
       </c>
       <c r="C55">
         <v>78.125</v>
@@ -5208,7 +5208,7 @@
         <v>78.125</v>
       </c>
       <c r="X55">
-        <v>0.13702</v>
+        <v>0.13705999999999999</v>
       </c>
       <c r="Y55">
         <v>78.125</v>
@@ -5234,7 +5234,7 @@
         <v>79.6875</v>
       </c>
       <c r="B56">
-        <v>0.13952000000000001</v>
+        <v>0.13982</v>
       </c>
       <c r="C56">
         <v>79.6875</v>
@@ -5306,7 +5306,7 @@
         <v>79.6875</v>
       </c>
       <c r="Z56">
-        <v>0.13977999999999999</v>
+        <v>0.13977000000000001</v>
       </c>
       <c r="AA56">
         <v>79.6875</v>
@@ -5326,7 +5326,7 @@
         <v>81.25</v>
       </c>
       <c r="B57">
-        <v>0.14230000000000001</v>
+        <v>0.14258000000000001</v>
       </c>
       <c r="C57">
         <v>81.25</v>
@@ -5392,19 +5392,19 @@
         <v>81.25</v>
       </c>
       <c r="X57">
-        <v>0.14251</v>
+        <v>0.14252000000000001</v>
       </c>
       <c r="Y57">
         <v>81.25</v>
       </c>
       <c r="Z57">
-        <v>0.14252999999999999</v>
+        <v>0.14249999999999999</v>
       </c>
       <c r="AA57">
         <v>81.25</v>
       </c>
       <c r="AB57">
-        <v>0.14255000000000001</v>
+        <v>0.14254</v>
       </c>
       <c r="AC57">
         <v>81.25</v>
@@ -5418,7 +5418,7 @@
         <v>82.8125</v>
       </c>
       <c r="B58">
-        <v>0.14502999999999999</v>
+        <v>0.14530999999999999</v>
       </c>
       <c r="C58">
         <v>82.8125</v>
@@ -5448,7 +5448,7 @@
         <v>82.8125</v>
       </c>
       <c r="L58">
-        <v>0.14524999999999999</v>
+        <v>0.14521000000000001</v>
       </c>
       <c r="M58">
         <v>82.8125</v>
@@ -5582,13 +5582,13 @@
         <v>84.375</v>
       </c>
       <c r="Z59">
-        <v>0.14802000000000001</v>
+        <v>0.14804999999999999</v>
       </c>
       <c r="AA59">
         <v>84.375</v>
       </c>
       <c r="AB59">
-        <v>0.14807000000000001</v>
+        <v>0.14807999999999999</v>
       </c>
       <c r="AC59">
         <v>84.375</v>
@@ -5668,19 +5668,19 @@
         <v>85.9375</v>
       </c>
       <c r="X60">
-        <v>0.15074000000000001</v>
+        <v>0.15075</v>
       </c>
       <c r="Y60">
         <v>85.9375</v>
       </c>
       <c r="Z60">
-        <v>0.15076000000000001</v>
+        <v>0.15081</v>
       </c>
       <c r="AA60">
         <v>85.9375</v>
       </c>
       <c r="AB60">
-        <v>0.15079999999999999</v>
+        <v>0.15081</v>
       </c>
       <c r="AC60">
         <v>85.9375</v>
@@ -5694,7 +5694,7 @@
         <v>87.5</v>
       </c>
       <c r="B61">
-        <v>0.15357999999999999</v>
+        <v>0.15359999999999999</v>
       </c>
       <c r="C61">
         <v>87.5</v>
@@ -5760,13 +5760,13 @@
         <v>87.5</v>
       </c>
       <c r="X61">
-        <v>0.15351999999999999</v>
+        <v>0.15351000000000001</v>
       </c>
       <c r="Y61">
         <v>87.5</v>
       </c>
       <c r="Z61">
-        <v>0.15354000000000001</v>
+        <v>0.15354999999999999</v>
       </c>
       <c r="AA61">
         <v>87.5</v>
@@ -5786,7 +5786,7 @@
         <v>89.0625</v>
       </c>
       <c r="B62">
-        <v>0.15636</v>
+        <v>0.15634000000000001</v>
       </c>
       <c r="C62">
         <v>89.0625</v>
@@ -5852,13 +5852,13 @@
         <v>89.0625</v>
       </c>
       <c r="X62">
-        <v>0.15625</v>
+        <v>0.15620999999999999</v>
       </c>
       <c r="Y62">
         <v>89.0625</v>
       </c>
       <c r="Z62">
-        <v>0.15626999999999999</v>
+        <v>0.15629999999999999</v>
       </c>
       <c r="AA62">
         <v>89.0625</v>
@@ -5878,7 +5878,7 @@
         <v>90.625</v>
       </c>
       <c r="B63">
-        <v>0.15909000000000001</v>
+        <v>0.15906999999999999</v>
       </c>
       <c r="C63">
         <v>90.625</v>
@@ -5944,13 +5944,13 @@
         <v>90.625</v>
       </c>
       <c r="X63">
-        <v>0.15901000000000001</v>
+        <v>0.15901999999999999</v>
       </c>
       <c r="Y63">
         <v>90.625</v>
       </c>
       <c r="Z63">
-        <v>0.15905</v>
+        <v>0.15903999999999999</v>
       </c>
       <c r="AA63">
         <v>90.625</v>
@@ -5962,7 +5962,7 @@
         <v>90.625</v>
       </c>
       <c r="AD63">
-        <v>0.15905</v>
+        <v>0.15909000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
@@ -5970,7 +5970,7 @@
         <v>92.1875</v>
       </c>
       <c r="B64">
-        <v>0.16187000000000001</v>
+        <v>0.16183</v>
       </c>
       <c r="C64">
         <v>92.1875</v>
@@ -6006,7 +6006,7 @@
         <v>92.1875</v>
       </c>
       <c r="N64">
-        <v>0.16178000000000001</v>
+        <v>0.16177</v>
       </c>
       <c r="O64">
         <v>92.1875</v>
@@ -6054,7 +6054,7 @@
         <v>92.1875</v>
       </c>
       <c r="AD64">
-        <v>0.16181000000000001</v>
+        <v>0.16181999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
@@ -6062,7 +6062,7 @@
         <v>93.75</v>
       </c>
       <c r="B65">
-        <v>0.16461000000000001</v>
+        <v>0.16458</v>
       </c>
       <c r="C65">
         <v>93.75</v>
@@ -6098,7 +6098,7 @@
         <v>93.75</v>
       </c>
       <c r="N65">
-        <v>0.16453999999999999</v>
+        <v>0.16450000000000001</v>
       </c>
       <c r="O65">
         <v>93.75</v>
@@ -6128,7 +6128,7 @@
         <v>93.75</v>
       </c>
       <c r="X65">
-        <v>0.16452</v>
+        <v>0.16455</v>
       </c>
       <c r="Y65">
         <v>93.75</v>
@@ -6154,7 +6154,7 @@
         <v>95.3125</v>
       </c>
       <c r="B66">
-        <v>0.16738</v>
+        <v>0.16732</v>
       </c>
       <c r="C66">
         <v>95.3125</v>
@@ -6220,25 +6220,25 @@
         <v>95.3125</v>
       </c>
       <c r="X66">
-        <v>0.16725000000000001</v>
+        <v>0.16725999999999999</v>
       </c>
       <c r="Y66">
         <v>95.3125</v>
       </c>
       <c r="Z66">
-        <v>0.16728000000000001</v>
+        <v>0.1673</v>
       </c>
       <c r="AA66">
         <v>95.3125</v>
       </c>
       <c r="AB66">
-        <v>0.16733999999999999</v>
+        <v>0.16739999999999999</v>
       </c>
       <c r="AC66">
         <v>95.3125</v>
       </c>
       <c r="AD66">
-        <v>0.16732</v>
+        <v>0.16730999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
@@ -6246,7 +6246,7 @@
         <v>96.875</v>
       </c>
       <c r="B67">
-        <v>0.17014000000000001</v>
+        <v>0.1701</v>
       </c>
       <c r="C67">
         <v>96.875</v>
@@ -6258,7 +6258,7 @@
         <v>96.875</v>
       </c>
       <c r="F67">
-        <v>0.17007</v>
+        <v>0.17008000000000001</v>
       </c>
       <c r="G67">
         <v>96.875</v>
@@ -6312,19 +6312,19 @@
         <v>96.875</v>
       </c>
       <c r="X67">
-        <v>0.17000999999999999</v>
+        <v>0.17002</v>
       </c>
       <c r="Y67">
         <v>96.875</v>
       </c>
       <c r="Z67">
-        <v>0.17005000000000001</v>
+        <v>0.17005999999999999</v>
       </c>
       <c r="AA67">
         <v>96.875</v>
       </c>
       <c r="AB67">
-        <v>0.1701</v>
+        <v>0.17011999999999999</v>
       </c>
       <c r="AC67">
         <v>96.875</v>
@@ -6338,7 +6338,7 @@
         <v>98.4375</v>
       </c>
       <c r="B68">
-        <v>0.17291999999999999</v>
+        <v>0.17285</v>
       </c>
       <c r="C68">
         <v>98.4375</v>
@@ -6404,13 +6404,13 @@
         <v>98.4375</v>
       </c>
       <c r="X68">
-        <v>0.17279</v>
+        <v>0.17277999999999999</v>
       </c>
       <c r="Y68">
         <v>98.4375</v>
       </c>
       <c r="Z68">
-        <v>0.17280999999999999</v>
+        <v>0.17282</v>
       </c>
       <c r="AA68">
         <v>98.4375</v>
@@ -6422,7 +6422,7 @@
         <v>98.4375</v>
       </c>
       <c r="AD68">
-        <v>0.17285</v>
+        <v>0.17280999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
@@ -6430,7 +6430,7 @@
         <v>100</v>
       </c>
       <c r="B69">
-        <v>0.17530999999999999</v>
+        <v>0.17524000000000001</v>
       </c>
       <c r="C69">
         <v>100</v>
@@ -6496,19 +6496,19 @@
         <v>100</v>
       </c>
       <c r="X69">
-        <v>0.17518</v>
+        <v>0.17519000000000001</v>
       </c>
       <c r="Y69">
         <v>100</v>
       </c>
       <c r="Z69">
-        <v>0.17519999999999999</v>
+        <v>0.1754</v>
       </c>
       <c r="AA69">
         <v>100</v>
       </c>
       <c r="AB69">
-        <v>0.17526</v>
+        <v>0.17530999999999999</v>
       </c>
       <c r="AC69">
         <v>100</v>
@@ -6522,7 +6522,7 @@
         <v>98.4375</v>
       </c>
       <c r="B70">
-        <v>0.17257</v>
+        <v>0.17252999999999999</v>
       </c>
       <c r="C70">
         <v>98.4375</v>
@@ -6588,13 +6588,13 @@
         <v>98.4375</v>
       </c>
       <c r="X70">
-        <v>0.17244000000000001</v>
+        <v>0.17244999999999999</v>
       </c>
       <c r="Y70">
         <v>98.4375</v>
       </c>
       <c r="Z70">
-        <v>0.17247000000000001</v>
+        <v>0.17247999999999999</v>
       </c>
       <c r="AA70">
         <v>98.4375</v>
@@ -6614,7 +6614,7 @@
         <v>96.875</v>
       </c>
       <c r="B71">
-        <v>0.16979</v>
+        <v>0.16972999999999999</v>
       </c>
       <c r="C71">
         <v>96.875</v>
@@ -6680,19 +6680,19 @@
         <v>96.875</v>
       </c>
       <c r="X71">
-        <v>0.16966999999999999</v>
+        <v>0.16968</v>
       </c>
       <c r="Y71">
         <v>96.875</v>
       </c>
       <c r="Z71">
-        <v>0.16969000000000001</v>
+        <v>0.16971</v>
       </c>
       <c r="AA71">
         <v>96.875</v>
       </c>
       <c r="AB71">
-        <v>0.16975000000000001</v>
+        <v>0.16977</v>
       </c>
       <c r="AC71">
         <v>96.875</v>
@@ -6706,7 +6706,7 @@
         <v>95.3125</v>
       </c>
       <c r="B72">
-        <v>0.16703999999999999</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="C72">
         <v>95.3125</v>
@@ -6778,7 +6778,7 @@
         <v>95.3125</v>
       </c>
       <c r="Z72">
-        <v>0.16693</v>
+        <v>0.16694999999999999</v>
       </c>
       <c r="AA72">
         <v>95.3125</v>
@@ -6798,7 +6798,7 @@
         <v>93.75</v>
       </c>
       <c r="B73">
-        <v>0.16428000000000001</v>
+        <v>0.16424</v>
       </c>
       <c r="C73">
         <v>93.75</v>
@@ -6864,13 +6864,13 @@
         <v>93.75</v>
       </c>
       <c r="X73">
-        <v>0.16414999999999999</v>
+        <v>0.16416</v>
       </c>
       <c r="Y73">
         <v>93.75</v>
       </c>
       <c r="Z73">
-        <v>0.16420000000000001</v>
+        <v>0.16420999999999999</v>
       </c>
       <c r="AA73">
         <v>93.75</v>
@@ -6890,7 +6890,7 @@
         <v>92.1875</v>
       </c>
       <c r="B74">
-        <v>0.16155</v>
+        <v>0.1615</v>
       </c>
       <c r="C74">
         <v>92.1875</v>
@@ -6908,7 +6908,7 @@
         <v>92.1875</v>
       </c>
       <c r="H74">
-        <v>0.16148000000000001</v>
+        <v>0.16150999999999999</v>
       </c>
       <c r="I74">
         <v>92.1875</v>
@@ -6956,7 +6956,7 @@
         <v>92.1875</v>
       </c>
       <c r="X74">
-        <v>0.16142000000000001</v>
+        <v>0.16145000000000001</v>
       </c>
       <c r="Y74">
         <v>92.1875</v>
@@ -6982,7 +6982,7 @@
         <v>90.625</v>
       </c>
       <c r="B75">
-        <v>0.15878999999999999</v>
+        <v>0.15873000000000001</v>
       </c>
       <c r="C75">
         <v>90.625</v>
@@ -7000,7 +7000,7 @@
         <v>90.625</v>
       </c>
       <c r="H75" s="1">
-        <v>0.15873000000000001</v>
+        <v>0.15876999999999999</v>
       </c>
       <c r="I75">
         <v>90.625</v>
@@ -7048,13 +7048,13 @@
         <v>90.625</v>
       </c>
       <c r="X75">
-        <v>0.15866</v>
+        <v>0.15862000000000001</v>
       </c>
       <c r="Y75">
         <v>90.625</v>
       </c>
       <c r="Z75">
-        <v>0.15867999999999999</v>
+        <v>0.15872</v>
       </c>
       <c r="AA75">
         <v>90.625</v>
@@ -7066,7 +7066,7 @@
         <v>90.625</v>
       </c>
       <c r="AD75">
-        <v>0.15873000000000001</v>
+        <v>0.15876999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:30" x14ac:dyDescent="0.25">
@@ -7074,7 +7074,7 @@
         <v>89.0625</v>
       </c>
       <c r="B76">
-        <v>0.15603</v>
+        <v>0.15598999999999999</v>
       </c>
       <c r="C76">
         <v>89.0625</v>
@@ -7086,7 +7086,7 @@
         <v>89.0625</v>
       </c>
       <c r="F76" s="1">
-        <v>0.15597</v>
+        <v>0.15593000000000001</v>
       </c>
       <c r="G76">
         <v>89.0625</v>
@@ -7140,13 +7140,13 @@
         <v>89.0625</v>
       </c>
       <c r="X76">
-        <v>0.15590999999999999</v>
+        <v>0.15590000000000001</v>
       </c>
       <c r="Y76">
         <v>89.0625</v>
       </c>
       <c r="Z76">
-        <v>0.15593000000000001</v>
+        <v>0.15595000000000001</v>
       </c>
       <c r="AA76">
         <v>89.0625</v>
@@ -7166,7 +7166,7 @@
         <v>87.5</v>
       </c>
       <c r="B77">
-        <v>0.15328</v>
+        <v>0.15323999999999999</v>
       </c>
       <c r="C77">
         <v>87.5</v>
@@ -7184,7 +7184,7 @@
         <v>87.5</v>
       </c>
       <c r="H77" s="1">
-        <v>0.15321000000000001</v>
+        <v>0.15325</v>
       </c>
       <c r="I77">
         <v>87.5</v>
@@ -7232,13 +7232,13 @@
         <v>87.5</v>
       </c>
       <c r="X77">
-        <v>0.15315000000000001</v>
+        <v>0.15318000000000001</v>
       </c>
       <c r="Y77">
         <v>87.5</v>
       </c>
       <c r="Z77">
-        <v>0.15317</v>
+        <v>0.15321000000000001</v>
       </c>
       <c r="AA77">
         <v>87.5</v>
@@ -7258,7 +7258,7 @@
         <v>85.9375</v>
       </c>
       <c r="B78">
-        <v>0.15051999999999999</v>
+        <v>0.15048</v>
       </c>
       <c r="C78">
         <v>85.9375</v>
@@ -7324,13 +7324,13 @@
         <v>85.9375</v>
       </c>
       <c r="X78">
-        <v>0.15040999999999999</v>
+        <v>0.15042</v>
       </c>
       <c r="Y78">
         <v>85.9375</v>
       </c>
       <c r="Z78">
-        <v>0.15040999999999999</v>
+        <v>0.15042</v>
       </c>
       <c r="AA78">
         <v>85.9375</v>
@@ -7342,7 +7342,7 @@
         <v>85.9375</v>
       </c>
       <c r="AD78">
-        <v>0.15048</v>
+        <v>0.15046000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.25">
@@ -7350,7 +7350,7 @@
         <v>84.375</v>
       </c>
       <c r="B79">
-        <v>0.14777000000000001</v>
+        <v>0.14774000000000001</v>
       </c>
       <c r="C79">
         <v>84.375</v>
@@ -7416,7 +7416,7 @@
         <v>84.375</v>
       </c>
       <c r="X79">
-        <v>0.14766000000000001</v>
+        <v>0.14765</v>
       </c>
       <c r="Y79">
         <v>84.375</v>
@@ -7428,13 +7428,13 @@
         <v>84.375</v>
       </c>
       <c r="AB79">
-        <v>0.14771999999999999</v>
+        <v>0.14777000000000001</v>
       </c>
       <c r="AC79">
         <v>84.375</v>
       </c>
       <c r="AD79">
-        <v>0.1477</v>
+        <v>0.14768000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:30" x14ac:dyDescent="0.25">
@@ -7442,7 +7442,7 @@
         <v>82.8125</v>
       </c>
       <c r="B80">
-        <v>0.14502999999999999</v>
+        <v>0.14496999999999999</v>
       </c>
       <c r="C80">
         <v>82.8125</v>
@@ -7508,7 +7508,7 @@
         <v>82.8125</v>
       </c>
       <c r="X80">
-        <v>0.1449</v>
+        <v>0.14510000000000001</v>
       </c>
       <c r="Y80">
         <v>82.8125</v>
@@ -7520,7 +7520,7 @@
         <v>82.8125</v>
       </c>
       <c r="AB80">
-        <v>0.14499000000000001</v>
+        <v>0.14498</v>
       </c>
       <c r="AC80">
         <v>82.8125</v>
@@ -7534,7 +7534,7 @@
         <v>81.25</v>
       </c>
       <c r="B81">
-        <v>0.14230000000000001</v>
+        <v>0.14223</v>
       </c>
       <c r="C81">
         <v>81.25</v>
@@ -7600,13 +7600,13 @@
         <v>81.25</v>
       </c>
       <c r="X81">
-        <v>0.14216999999999999</v>
+        <v>0.14213999999999999</v>
       </c>
       <c r="Y81">
         <v>81.25</v>
       </c>
       <c r="Z81">
-        <v>0.14216999999999999</v>
+        <v>0.14218</v>
       </c>
       <c r="AA81">
         <v>81.25</v>
@@ -7626,7 +7626,7 @@
         <v>79.6875</v>
       </c>
       <c r="B82">
-        <v>0.13952000000000001</v>
+        <v>0.13950000000000001</v>
       </c>
       <c r="C82">
         <v>79.6875</v>
@@ -7692,19 +7692,19 @@
         <v>79.6875</v>
       </c>
       <c r="X82">
-        <v>0.13941000000000001</v>
+        <v>0.13943</v>
       </c>
       <c r="Y82">
         <v>79.6875</v>
       </c>
       <c r="Z82">
-        <v>0.13943</v>
+        <v>0.13941999999999999</v>
       </c>
       <c r="AA82">
         <v>79.6875</v>
       </c>
       <c r="AB82">
-        <v>0.13950000000000001</v>
+        <v>0.13980000000000001</v>
       </c>
       <c r="AC82">
         <v>79.6875</v>
@@ -7718,7 +7718,7 @@
         <v>78.125</v>
       </c>
       <c r="B83">
-        <v>0.13678000000000001</v>
+        <v>0.13674</v>
       </c>
       <c r="C83">
         <v>78.125</v>
@@ -7802,7 +7802,7 @@
         <v>78.125</v>
       </c>
       <c r="AD83">
-        <v>0.13672000000000001</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="84" spans="1:30" x14ac:dyDescent="0.25">
@@ -7810,7 +7810,7 @@
         <v>76.5625</v>
       </c>
       <c r="B84">
-        <v>0.13403000000000001</v>
+        <v>0.13397999999999999</v>
       </c>
       <c r="C84">
         <v>76.5625</v>
@@ -7882,7 +7882,7 @@
         <v>76.5625</v>
       </c>
       <c r="Z84" s="1">
-        <v>0.13394</v>
+        <v>0.13389999999999999</v>
       </c>
       <c r="AA84">
         <v>76.5625</v>
@@ -7894,7 +7894,7 @@
         <v>76.5625</v>
       </c>
       <c r="AD84">
-        <v>0.13396</v>
+        <v>0.13399</v>
       </c>
     </row>
     <row r="85" spans="1:30" x14ac:dyDescent="0.25">
@@ -7902,7 +7902,7 @@
         <v>75</v>
       </c>
       <c r="B85">
-        <v>0.13128999999999999</v>
+        <v>0.13125000000000001</v>
       </c>
       <c r="C85">
         <v>75</v>
@@ -7956,7 +7956,7 @@
         <v>75</v>
       </c>
       <c r="T85" s="1">
-        <v>0.13120999999999999</v>
+        <v>0.13117000000000001</v>
       </c>
       <c r="U85">
         <v>75</v>
@@ -7986,7 +7986,7 @@
         <v>75</v>
       </c>
       <c r="AD85">
-        <v>0.13125000000000001</v>
+        <v>0.13127</v>
       </c>
     </row>
     <row r="86" spans="1:30" x14ac:dyDescent="0.25">
@@ -7994,7 +7994,7 @@
         <v>73.4375</v>
       </c>
       <c r="B86">
-        <v>0.12856000000000001</v>
+        <v>0.12851000000000001</v>
       </c>
       <c r="C86">
         <v>73.4375</v>
@@ -8006,7 +8006,7 @@
         <v>73.4375</v>
       </c>
       <c r="F86" s="1">
-        <v>0.12851000000000001</v>
+        <v>0.12853000000000001</v>
       </c>
       <c r="G86">
         <v>73.4375</v>
@@ -8018,7 +8018,7 @@
         <v>73.4375</v>
       </c>
       <c r="J86">
-        <v>0.12848999999999999</v>
+        <v>0.12851000000000001</v>
       </c>
       <c r="K86">
         <v>73.4375</v>
@@ -8048,7 +8048,7 @@
         <v>73.4375</v>
       </c>
       <c r="T86" s="1">
-        <v>0.12847</v>
+        <v>0.12848999999999999</v>
       </c>
       <c r="U86">
         <v>73.4375</v>
@@ -8060,13 +8060,13 @@
         <v>73.4375</v>
       </c>
       <c r="X86">
-        <v>0.12845000000000001</v>
+        <v>0.12848000000000001</v>
       </c>
       <c r="Y86">
         <v>73.4375</v>
       </c>
       <c r="Z86">
-        <v>0.12847</v>
+        <v>0.12845000000000001</v>
       </c>
       <c r="AA86">
         <v>73.4375</v>
@@ -8086,7 +8086,7 @@
         <v>71.875</v>
       </c>
       <c r="B87">
-        <v>0.1258</v>
+        <v>0.12576000000000001</v>
       </c>
       <c r="C87">
         <v>71.875</v>
@@ -8110,7 +8110,7 @@
         <v>71.875</v>
       </c>
       <c r="J87">
-        <v>0.12573999999999999</v>
+        <v>0.12576000000000001</v>
       </c>
       <c r="K87">
         <v>71.875</v>
@@ -8152,13 +8152,13 @@
         <v>71.875</v>
       </c>
       <c r="X87">
-        <v>0.12569</v>
+        <v>0.12570999999999999</v>
       </c>
       <c r="Y87">
         <v>71.875</v>
       </c>
       <c r="Z87">
-        <v>0.12572</v>
+        <v>0.12573000000000001</v>
       </c>
       <c r="AA87">
         <v>71.875</v>
@@ -8178,7 +8178,7 @@
         <v>70.3125</v>
       </c>
       <c r="B88">
-        <v>0.12307</v>
+        <v>0.123</v>
       </c>
       <c r="C88">
         <v>70.3125</v>
@@ -8202,7 +8202,7 @@
         <v>70.3125</v>
       </c>
       <c r="J88">
-        <v>0.12298000000000001</v>
+        <v>0.12295</v>
       </c>
       <c r="K88">
         <v>70.3125</v>
@@ -8244,13 +8244,13 @@
         <v>70.3125</v>
       </c>
       <c r="X88">
-        <v>0.12296</v>
+        <v>0.12299</v>
       </c>
       <c r="Y88">
         <v>70.3125</v>
       </c>
       <c r="Z88">
-        <v>0.12296</v>
+        <v>0.12295</v>
       </c>
       <c r="AA88">
         <v>70.3125</v>
@@ -8270,7 +8270,7 @@
         <v>68.75</v>
       </c>
       <c r="B89">
-        <v>0.12031</v>
+        <v>0.12027</v>
       </c>
       <c r="C89">
         <v>68.75</v>
@@ -8294,7 +8294,7 @@
         <v>68.75</v>
       </c>
       <c r="J89">
-        <v>0.12025</v>
+        <v>0.12023</v>
       </c>
       <c r="K89">
         <v>68.75</v>
@@ -8336,7 +8336,7 @@
         <v>68.75</v>
       </c>
       <c r="X89">
-        <v>0.12021999999999999</v>
+        <v>0.12021</v>
       </c>
       <c r="Y89">
         <v>68.75</v>
@@ -8362,7 +8362,7 @@
         <v>67.1875</v>
       </c>
       <c r="B90">
-        <v>0.11758</v>
+        <v>0.11753</v>
       </c>
       <c r="C90">
         <v>67.1875</v>
@@ -8434,7 +8434,7 @@
         <v>67.1875</v>
       </c>
       <c r="Z90">
-        <v>0.11747</v>
+        <v>0.11748</v>
       </c>
       <c r="AA90">
         <v>67.1875</v>
@@ -8446,7 +8446,7 @@
         <v>67.1875</v>
       </c>
       <c r="AD90">
-        <v>0.11753</v>
+        <v>0.11756999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:30" x14ac:dyDescent="0.25">
@@ -8454,7 +8454,7 @@
         <v>65.625</v>
       </c>
       <c r="B91">
-        <v>0.11482000000000001</v>
+        <v>0.11477999999999999</v>
       </c>
       <c r="C91">
         <v>65.625</v>
@@ -8520,7 +8520,7 @@
         <v>65.625</v>
       </c>
       <c r="X91">
-        <v>0.11471000000000001</v>
+        <v>0.1147</v>
       </c>
       <c r="Y91">
         <v>65.625</v>
@@ -8546,7 +8546,7 @@
         <v>64.0625</v>
       </c>
       <c r="B92">
-        <v>0.11208</v>
+        <v>0.11204</v>
       </c>
       <c r="C92">
         <v>64.0625</v>
@@ -8564,7 +8564,7 @@
         <v>64.0625</v>
       </c>
       <c r="H92">
-        <v>0.112</v>
+        <v>0.1118</v>
       </c>
       <c r="I92">
         <v>64.0625</v>
@@ -8618,7 +8618,7 @@
         <v>64.0625</v>
       </c>
       <c r="Z92">
-        <v>0.112</v>
+        <v>0.11219999999999999</v>
       </c>
       <c r="AA92">
         <v>64.0625</v>
@@ -8630,7 +8630,7 @@
         <v>64.0625</v>
       </c>
       <c r="AD92">
-        <v>0.11204</v>
+        <v>0.11207</v>
       </c>
     </row>
     <row r="93" spans="1:30" x14ac:dyDescent="0.25">
@@ -8638,7 +8638,7 @@
         <v>62.5</v>
       </c>
       <c r="B93">
-        <v>0.10935</v>
+        <v>0.10928</v>
       </c>
       <c r="C93">
         <v>62.5</v>
@@ -8656,7 +8656,7 @@
         <v>62.5</v>
       </c>
       <c r="H93">
-        <v>0.10924</v>
+        <v>0.10922</v>
       </c>
       <c r="I93">
         <v>62.5</v>
@@ -8668,7 +8668,7 @@
         <v>62.5</v>
       </c>
       <c r="L93">
-        <v>0.10924</v>
+        <v>0.10926</v>
       </c>
       <c r="M93">
         <v>62.5</v>
@@ -8730,7 +8730,7 @@
         <v>60.9375</v>
       </c>
       <c r="B94">
-        <v>0.10659</v>
+        <v>0.10653</v>
       </c>
       <c r="C94">
         <v>60.9375</v>
@@ -8748,7 +8748,7 @@
         <v>60.9375</v>
       </c>
       <c r="H94">
-        <v>0.10650999999999999</v>
+        <v>0.10649</v>
       </c>
       <c r="I94">
         <v>60.9375</v>
@@ -8796,13 +8796,13 @@
         <v>60.9375</v>
       </c>
       <c r="X94">
-        <v>0.10649</v>
+        <v>0.10653</v>
       </c>
       <c r="Y94">
         <v>60.9375</v>
       </c>
       <c r="Z94">
-        <v>0.10649</v>
+        <v>0.10650999999999999</v>
       </c>
       <c r="AA94">
         <v>60.9375</v>
@@ -8814,7 +8814,7 @@
         <v>60.9375</v>
       </c>
       <c r="AD94">
-        <v>0.10655000000000001</v>
+        <v>0.10657</v>
       </c>
     </row>
     <row r="95" spans="1:30" x14ac:dyDescent="0.25">
@@ -8822,7 +8822,7 @@
         <v>59.375</v>
       </c>
       <c r="B95">
-        <v>0.10384</v>
+        <v>0.10378999999999999</v>
       </c>
       <c r="C95">
         <v>59.375</v>
@@ -8840,7 +8840,7 @@
         <v>59.375</v>
       </c>
       <c r="H95">
-        <v>0.10375</v>
+        <v>0.10377</v>
       </c>
       <c r="I95">
         <v>59.375</v>
@@ -8888,7 +8888,7 @@
         <v>59.375</v>
       </c>
       <c r="X95">
-        <v>0.10373</v>
+        <v>0.10377</v>
       </c>
       <c r="Y95">
         <v>59.375</v>
@@ -8906,7 +8906,7 @@
         <v>59.375</v>
       </c>
       <c r="AD95">
-        <v>0.10378999999999999</v>
+        <v>0.10381</v>
       </c>
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.25">
@@ -8914,7 +8914,7 @@
         <v>57.8125</v>
       </c>
       <c r="B96">
-        <v>0.1011</v>
+        <v>0.10104</v>
       </c>
       <c r="C96">
         <v>57.8125</v>
@@ -8980,13 +8980,13 @@
         <v>57.8125</v>
       </c>
       <c r="X96">
-        <v>0.10099</v>
+        <v>0.10098</v>
       </c>
       <c r="Y96">
         <v>57.8125</v>
       </c>
       <c r="Z96">
-        <v>0.10102</v>
+        <v>0.10102999999999999</v>
       </c>
       <c r="AA96">
         <v>57.8125</v>
@@ -9006,7 +9006,7 @@
         <v>56.25</v>
       </c>
       <c r="B97">
-        <v>9.8369999999999999E-2</v>
+        <v>9.8299999999999998E-2</v>
       </c>
       <c r="C97">
         <v>56.25</v>
@@ -9024,7 +9024,7 @@
         <v>56.25</v>
       </c>
       <c r="H97">
-        <v>9.8280000000000006E-2</v>
+        <v>9.8250000000000004E-2</v>
       </c>
       <c r="I97">
         <v>56.25</v>
@@ -9042,7 +9042,7 @@
         <v>56.25</v>
       </c>
       <c r="N97" s="1">
-        <v>9.8280000000000006E-2</v>
+        <v>9.8309999999999995E-2</v>
       </c>
       <c r="O97">
         <v>56.25</v>
@@ -9072,13 +9072,13 @@
         <v>56.25</v>
       </c>
       <c r="X97">
-        <v>9.8280000000000006E-2</v>
+        <v>9.8269999999999996E-2</v>
       </c>
       <c r="Y97">
         <v>56.25</v>
       </c>
       <c r="Z97">
-        <v>9.8280000000000006E-2</v>
+        <v>9.8320000000000005E-2</v>
       </c>
       <c r="AA97">
         <v>56.25</v>
@@ -9098,7 +9098,7 @@
         <v>54.6875</v>
       </c>
       <c r="B98">
-        <v>9.5610000000000001E-2</v>
+        <v>9.5570000000000002E-2</v>
       </c>
       <c r="C98">
         <v>54.6875</v>
@@ -9134,7 +9134,7 @@
         <v>54.6875</v>
       </c>
       <c r="N98" s="1">
-        <v>9.5519999999999994E-2</v>
+        <v>9.5530000000000004E-2</v>
       </c>
       <c r="O98">
         <v>54.6875</v>
@@ -9152,7 +9152,7 @@
         <v>54.6875</v>
       </c>
       <c r="T98">
-        <v>9.5549999999999996E-2</v>
+        <v>9.5560000000000006E-2</v>
       </c>
       <c r="U98">
         <v>54.6875</v>
@@ -9164,13 +9164,13 @@
         <v>54.6875</v>
       </c>
       <c r="X98">
-        <v>9.5519999999999994E-2</v>
+        <v>9.5579999999999998E-2</v>
       </c>
       <c r="Y98">
         <v>54.6875</v>
       </c>
       <c r="Z98">
-        <v>9.5519999999999994E-2</v>
+        <v>9.5530000000000004E-2</v>
       </c>
       <c r="AA98">
         <v>54.6875</v>
@@ -9190,7 +9190,7 @@
         <v>53.125</v>
       </c>
       <c r="B99">
-        <v>9.2899999999999996E-2</v>
+        <v>9.2829999999999996E-2</v>
       </c>
       <c r="C99">
         <v>53.125</v>
@@ -9226,7 +9226,7 @@
         <v>53.125</v>
       </c>
       <c r="N99">
-        <v>9.2789999999999997E-2</v>
+        <v>9.2810000000000004E-2</v>
       </c>
       <c r="O99">
         <v>53.125</v>
@@ -9244,7 +9244,7 @@
         <v>53.125</v>
       </c>
       <c r="T99">
-        <v>9.2789999999999997E-2</v>
+        <v>9.2799999999999994E-2</v>
       </c>
       <c r="U99">
         <v>53.125</v>
@@ -9256,13 +9256,13 @@
         <v>53.125</v>
       </c>
       <c r="X99">
-        <v>9.2789999999999997E-2</v>
+        <v>9.2780000000000001E-2</v>
       </c>
       <c r="Y99">
         <v>53.125</v>
       </c>
       <c r="Z99">
-        <v>9.2789999999999997E-2</v>
+        <v>9.2829999999999996E-2</v>
       </c>
       <c r="AA99">
         <v>53.125</v>
@@ -9282,7 +9282,7 @@
         <v>51.5625</v>
       </c>
       <c r="B100">
-        <v>9.0139999999999998E-2</v>
+        <v>9.0079999999999993E-2</v>
       </c>
       <c r="C100">
         <v>51.5625</v>
@@ -9318,7 +9318,7 @@
         <v>51.5625</v>
       </c>
       <c r="N100">
-        <v>9.0050000000000005E-2</v>
+        <v>9.0069999999999997E-2</v>
       </c>
       <c r="O100">
         <v>51.5625</v>
@@ -9336,7 +9336,7 @@
         <v>51.5625</v>
       </c>
       <c r="T100">
-        <v>9.0050000000000005E-2</v>
+        <v>9.0060000000000001E-2</v>
       </c>
       <c r="U100">
         <v>51.5625</v>
@@ -9348,13 +9348,13 @@
         <v>51.5625</v>
       </c>
       <c r="X100">
-        <v>9.0050000000000005E-2</v>
+        <v>9.0060000000000001E-2</v>
       </c>
       <c r="Y100">
         <v>51.5625</v>
       </c>
       <c r="Z100">
-        <v>9.0050000000000005E-2</v>
+        <v>9.0069999999999997E-2</v>
       </c>
       <c r="AA100">
         <v>51.5625</v>
@@ -9374,7 +9374,7 @@
         <v>50</v>
       </c>
       <c r="B101">
-        <v>8.7319999999999995E-2</v>
+        <v>8.7260000000000004E-2</v>
       </c>
       <c r="C101">
         <v>50</v>
@@ -9428,7 +9428,7 @@
         <v>50</v>
       </c>
       <c r="T101">
-        <v>8.7230000000000002E-2</v>
+        <v>8.7249999999999994E-2</v>
       </c>
       <c r="U101">
         <v>50</v>
@@ -9446,7 +9446,7 @@
         <v>50</v>
       </c>
       <c r="Z101">
-        <v>8.7230000000000002E-2</v>
+        <v>8.7260000000000004E-2</v>
       </c>
       <c r="AA101">
         <v>50</v>
@@ -9466,7 +9466,7 @@
         <v>48.4375</v>
       </c>
       <c r="B102">
-        <v>8.4559999999999996E-2</v>
+        <v>8.4519999999999998E-2</v>
       </c>
       <c r="C102">
         <v>48.4375</v>
@@ -9502,7 +9502,7 @@
         <v>48.4375</v>
       </c>
       <c r="N102">
-        <v>8.4500000000000006E-2</v>
+        <v>8.4510000000000002E-2</v>
       </c>
       <c r="O102">
         <v>48.4375</v>
@@ -9520,7 +9520,7 @@
         <v>48.4375</v>
       </c>
       <c r="T102">
-        <v>8.4500000000000006E-2</v>
+        <v>8.4510000000000002E-2</v>
       </c>
       <c r="U102">
         <v>48.4375</v>
@@ -9532,13 +9532,13 @@
         <v>48.4375</v>
       </c>
       <c r="X102">
-        <v>8.4500000000000006E-2</v>
+        <v>8.4519999999999998E-2</v>
       </c>
       <c r="Y102">
         <v>48.4375</v>
       </c>
       <c r="Z102">
-        <v>8.4500000000000006E-2</v>
+        <v>8.4409999999999999E-2</v>
       </c>
       <c r="AA102">
         <v>48.4375</v>
@@ -9558,7 +9558,7 @@
         <v>46.875</v>
       </c>
       <c r="B103">
-        <v>8.183E-2</v>
+        <v>8.1759999999999999E-2</v>
       </c>
       <c r="C103">
         <v>46.875</v>
@@ -9594,7 +9594,7 @@
         <v>46.875</v>
       </c>
       <c r="N103">
-        <v>8.1739999999999993E-2</v>
+        <v>8.1759999999999999E-2</v>
       </c>
       <c r="O103">
         <v>46.875</v>
@@ -9612,7 +9612,7 @@
         <v>46.875</v>
       </c>
       <c r="T103">
-        <v>8.1739999999999993E-2</v>
+        <v>8.1750000000000003E-2</v>
       </c>
       <c r="U103">
         <v>46.875</v>
@@ -9624,13 +9624,13 @@
         <v>46.875</v>
       </c>
       <c r="X103">
-        <v>8.1739999999999993E-2</v>
+        <v>8.1769999999999995E-2</v>
       </c>
       <c r="Y103">
         <v>46.875</v>
       </c>
       <c r="Z103">
-        <v>8.1739999999999993E-2</v>
+        <v>8.1720000000000001E-2</v>
       </c>
       <c r="AA103">
         <v>46.875</v>
@@ -9650,7 +9650,7 @@
         <v>45.3125</v>
       </c>
       <c r="B104">
-        <v>7.9070000000000001E-2</v>
+        <v>7.9049999999999995E-2</v>
       </c>
       <c r="C104">
         <v>45.3125</v>
@@ -9686,7 +9686,7 @@
         <v>45.3125</v>
       </c>
       <c r="N104">
-        <v>7.9009999999999997E-2</v>
+        <v>7.9030000000000003E-2</v>
       </c>
       <c r="O104">
         <v>45.3125</v>
@@ -9704,7 +9704,7 @@
         <v>45.3125</v>
       </c>
       <c r="T104">
-        <v>7.9009999999999997E-2</v>
+        <v>7.9020000000000007E-2</v>
       </c>
       <c r="U104">
         <v>45.3125</v>
@@ -9722,7 +9722,7 @@
         <v>45.3125</v>
       </c>
       <c r="Z104">
-        <v>7.9009999999999997E-2</v>
+        <v>7.9020000000000007E-2</v>
       </c>
       <c r="AA104">
         <v>45.3125</v>
@@ -9742,7 +9742,7 @@
         <v>43.75</v>
       </c>
       <c r="B105">
-        <v>7.6340000000000005E-2</v>
+        <v>7.6270000000000004E-2</v>
       </c>
       <c r="C105" s="1">
         <v>43.75</v>
@@ -9778,7 +9778,7 @@
         <v>43.75</v>
       </c>
       <c r="N105">
-        <v>7.6270000000000004E-2</v>
+        <v>7.6289999999999997E-2</v>
       </c>
       <c r="O105">
         <v>43.75</v>
@@ -9796,7 +9796,7 @@
         <v>43.75</v>
       </c>
       <c r="T105">
-        <v>7.6270000000000004E-2</v>
+        <v>7.6300000000000007E-2</v>
       </c>
       <c r="U105">
         <v>43.75</v>
@@ -9808,13 +9808,13 @@
         <v>43.75</v>
       </c>
       <c r="X105">
-        <v>7.6270000000000004E-2</v>
+        <v>7.6280000000000001E-2</v>
       </c>
       <c r="Y105">
         <v>43.75</v>
       </c>
       <c r="Z105">
-        <v>7.6270000000000004E-2</v>
+        <v>7.6280000000000001E-2</v>
       </c>
       <c r="AA105">
         <v>43.75</v>
@@ -9834,7 +9834,7 @@
         <v>42.1875</v>
       </c>
       <c r="B106">
-        <v>7.3539999999999994E-2</v>
+        <v>7.356E-2</v>
       </c>
       <c r="C106" s="1">
         <v>42.1875</v>
@@ -9870,7 +9870,7 @@
         <v>42.1875</v>
       </c>
       <c r="N106">
-        <v>7.3539999999999994E-2</v>
+        <v>7.356E-2</v>
       </c>
       <c r="O106">
         <v>42.1875</v>
@@ -9888,7 +9888,7 @@
         <v>42.1875</v>
       </c>
       <c r="T106">
-        <v>7.3539999999999994E-2</v>
+        <v>7.3569999999999997E-2</v>
       </c>
       <c r="U106">
         <v>42.1875</v>
@@ -9900,13 +9900,13 @@
         <v>42.1875</v>
       </c>
       <c r="X106">
-        <v>7.3539999999999994E-2</v>
+        <v>7.3550000000000004E-2</v>
       </c>
       <c r="Y106">
         <v>42.1875</v>
       </c>
       <c r="Z106">
-        <v>7.3539999999999994E-2</v>
+        <v>7.3550000000000004E-2</v>
       </c>
       <c r="AA106">
         <v>42.1875</v>
@@ -9926,7 +9926,7 @@
         <v>40.625</v>
       </c>
       <c r="B107">
-        <v>7.0220000000000005E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="C107">
         <v>40.625</v>
@@ -9980,7 +9980,7 @@
         <v>40.625</v>
       </c>
       <c r="T107">
-        <v>7.0779999999999996E-2</v>
+        <v>7.077E-2</v>
       </c>
       <c r="U107">
         <v>40.625</v>
@@ -9992,7 +9992,7 @@
         <v>40.625</v>
       </c>
       <c r="X107">
-        <v>7.0779999999999996E-2</v>
+        <v>7.0739999999999997E-2</v>
       </c>
       <c r="Y107">
         <v>40.625</v>
@@ -10018,7 +10018,7 @@
         <v>39.0625</v>
       </c>
       <c r="B108">
-        <v>6.6850000000000007E-2</v>
+        <v>6.8049999999999999E-2</v>
       </c>
       <c r="C108">
         <v>39.0625</v>
@@ -10072,7 +10072,7 @@
         <v>39.0625</v>
       </c>
       <c r="T108">
-        <v>6.8049999999999999E-2</v>
+        <v>6.8059999999999996E-2</v>
       </c>
       <c r="U108">
         <v>39.0625</v>
@@ -10110,7 +10110,7 @@
         <v>37.5</v>
       </c>
       <c r="B109">
-        <v>6.3479999999999995E-2</v>
+        <v>6.5180000000000002E-2</v>
       </c>
       <c r="C109" s="1">
         <v>37.5</v>
@@ -10140,7 +10140,7 @@
         <v>37.5</v>
       </c>
       <c r="L109">
-        <v>6.5290000000000001E-2</v>
+        <v>6.5329999999999999E-2</v>
       </c>
       <c r="M109">
         <v>37.5</v>
@@ -10164,7 +10164,7 @@
         <v>37.5</v>
       </c>
       <c r="T109">
-        <v>6.5290000000000001E-2</v>
+        <v>6.5310000000000007E-2</v>
       </c>
       <c r="U109">
         <v>37.5</v>
@@ -10182,7 +10182,7 @@
         <v>37.5</v>
       </c>
       <c r="Z109">
-        <v>6.5310000000000007E-2</v>
+        <v>6.5259999999999999E-2</v>
       </c>
       <c r="AA109">
         <v>37.5</v>
@@ -10202,7 +10202,7 @@
         <v>35.9375</v>
       </c>
       <c r="B110">
-        <v>6.0269999999999997E-2</v>
+        <v>6.1310000000000003E-2</v>
       </c>
       <c r="C110" s="1">
         <v>35.9375</v>
@@ -10268,7 +10268,7 @@
         <v>35.9375</v>
       </c>
       <c r="X110">
-        <v>6.2560000000000004E-2</v>
+        <v>6.2570000000000001E-2</v>
       </c>
       <c r="Y110">
         <v>35.9375</v>
@@ -10294,7 +10294,7 @@
         <v>34.375</v>
       </c>
       <c r="B111">
-        <v>5.7200000000000001E-2</v>
+        <v>5.2650000000000002E-2</v>
       </c>
       <c r="C111" s="1">
         <v>34.375</v>
@@ -10360,13 +10360,13 @@
         <v>34.375</v>
       </c>
       <c r="X111">
-        <v>5.9799999999999999E-2</v>
+        <v>5.9810000000000002E-2</v>
       </c>
       <c r="Y111">
         <v>34.375</v>
       </c>
       <c r="Z111">
-        <v>5.9799999999999999E-2</v>
+        <v>5.9810000000000002E-2</v>
       </c>
       <c r="AA111">
         <v>34.375</v>
@@ -10386,7 +10386,7 @@
         <v>32.8125</v>
       </c>
       <c r="B112" s="1">
-        <v>5.4260000000000003E-2</v>
+        <v>2.48E-3</v>
       </c>
       <c r="C112" s="1">
         <v>32.8125</v>
@@ -10478,7 +10478,7 @@
         <v>31.25</v>
       </c>
       <c r="B113">
-        <v>5.1189999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C113" s="1">
         <v>31.25</v>
@@ -10544,13 +10544,13 @@
         <v>31.25</v>
       </c>
       <c r="X113">
-        <v>5.4330000000000003E-2</v>
+        <v>5.432E-2</v>
       </c>
       <c r="Y113">
         <v>31.25</v>
       </c>
       <c r="Z113">
-        <v>5.4330000000000003E-2</v>
+        <v>5.432E-2</v>
       </c>
       <c r="AA113">
         <v>31.25</v>
@@ -10570,7 +10570,7 @@
         <v>29.6875</v>
       </c>
       <c r="B114">
-        <v>4.8379999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C114" s="1">
         <v>29.6875</v>
@@ -10636,7 +10636,7 @@
         <v>29.6875</v>
       </c>
       <c r="X114">
-        <v>5.1549999999999999E-2</v>
+        <v>5.1540000000000002E-2</v>
       </c>
       <c r="Y114">
         <v>29.6875</v>
@@ -10662,7 +10662,7 @@
         <v>28.125</v>
       </c>
       <c r="B115">
-        <v>4.5569999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C115" s="1">
         <v>28.125</v>
@@ -10728,13 +10728,13 @@
         <v>28.125</v>
       </c>
       <c r="X115">
-        <v>4.8579999999999998E-2</v>
+        <v>4.8550000000000003E-2</v>
       </c>
       <c r="Y115">
         <v>28.125</v>
       </c>
       <c r="Z115">
-        <v>4.8579999999999998E-2</v>
+        <v>4.8500000000000001E-2</v>
       </c>
       <c r="AA115">
         <v>28.125</v>
@@ -10754,7 +10754,7 @@
         <v>26.5625</v>
       </c>
       <c r="B116">
-        <v>4.2500000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C116" s="1">
         <v>26.5625</v>
@@ -10820,7 +10820,7 @@
         <v>26.5625</v>
       </c>
       <c r="X116">
-        <v>4.4810000000000003E-2</v>
+        <v>4.4819999999999999E-2</v>
       </c>
       <c r="Y116">
         <v>26.5625</v>
@@ -10846,7 +10846,7 @@
         <v>25</v>
       </c>
       <c r="B117">
-        <v>3.9419999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C117" s="1">
         <v>25</v>
@@ -10938,7 +10938,7 @@
         <v>23.4375</v>
       </c>
       <c r="B118">
-        <v>3.6650000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C118" s="1">
         <v>23.4375</v>
@@ -14319,7 +14319,7 @@
         <v>-32.8125</v>
       </c>
       <c r="X154">
-        <v>-5.7520000000000002E-2</v>
+        <v>-5.7549999999999997E-2</v>
       </c>
       <c r="Y154">
         <v>-32.8125</v>
@@ -14417,7 +14417,7 @@
         <v>-34.375</v>
       </c>
       <c r="Z155">
-        <v>-6.0249999999999998E-2</v>
+        <v>-6.0310000000000002E-2</v>
       </c>
       <c r="AA155">
         <v>-34.375</v>
@@ -14509,7 +14509,7 @@
         <v>-35.9375</v>
       </c>
       <c r="Z156">
-        <v>-6.3009999999999997E-2</v>
+        <v>-6.3020000000000007E-2</v>
       </c>
       <c r="AA156">
         <v>-35.9375</v>
@@ -14681,7 +14681,7 @@
         <v>-39.0625</v>
       </c>
       <c r="V158">
-        <v>-6.8500000000000005E-2</v>
+        <v>-6.7900000000000002E-2</v>
       </c>
       <c r="W158">
         <v>-39.0625</v>
@@ -14693,7 +14693,7 @@
         <v>-39.0625</v>
       </c>
       <c r="Z158">
-        <v>-6.8500000000000005E-2</v>
+        <v>-6.855E-2</v>
       </c>
       <c r="AA158">
         <v>-39.0625</v>
@@ -14773,7 +14773,7 @@
         <v>-40.625</v>
       </c>
       <c r="V159">
-        <v>-7.1209999999999996E-2</v>
+        <v>-7.1199999999999999E-2</v>
       </c>
       <c r="W159">
         <v>-40.625</v>
@@ -14785,7 +14785,7 @@
         <v>-40.625</v>
       </c>
       <c r="Z159">
-        <v>-7.1209999999999996E-2</v>
+        <v>-7.1199999999999999E-2</v>
       </c>
       <c r="AA159">
         <v>-40.625</v>
@@ -14865,7 +14865,7 @@
         <v>-42.1875</v>
       </c>
       <c r="V160">
-        <v>-7.3969999999999994E-2</v>
+        <v>-7.3980000000000004E-2</v>
       </c>
       <c r="W160">
         <v>-42.1875</v>
@@ -14889,7 +14889,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AD160">
-        <v>-7.399E-2</v>
+        <v>-7.3980000000000004E-2</v>
       </c>
     </row>
     <row r="161" spans="1:30" x14ac:dyDescent="0.25">
@@ -14957,7 +14957,7 @@
         <v>-43.75</v>
       </c>
       <c r="V161">
-        <v>-7.6700000000000004E-2</v>
+        <v>-7.6799999999999993E-2</v>
       </c>
       <c r="W161">
         <v>-43.75</v>
@@ -14981,7 +14981,7 @@
         <v>-43.75</v>
       </c>
       <c r="AD161">
-        <v>-7.6700000000000004E-2</v>
+        <v>-7.6799999999999993E-2</v>
       </c>
     </row>
     <row r="162" spans="1:30" x14ac:dyDescent="0.25">
@@ -15073,7 +15073,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AD162">
-        <v>-7.9460000000000003E-2</v>
+        <v>-7.9509999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="1:30" x14ac:dyDescent="0.25">
@@ -15129,7 +15129,7 @@
         <v>-46.875</v>
       </c>
       <c r="R163">
-        <v>-8.2110000000000002E-2</v>
+        <v>-8.2059999999999994E-2</v>
       </c>
       <c r="S163">
         <v>-46.875</v>
@@ -15141,7 +15141,7 @@
         <v>-46.875</v>
       </c>
       <c r="V163">
-        <v>-8.2170000000000007E-2</v>
+        <v>-8.2210000000000005E-2</v>
       </c>
       <c r="W163">
         <v>-46.875</v>
@@ -15153,7 +15153,7 @@
         <v>-46.875</v>
       </c>
       <c r="Z163">
-        <v>-8.2189999999999999E-2</v>
+        <v>-8.2150000000000001E-2</v>
       </c>
       <c r="AA163">
         <v>-46.875</v>
@@ -15221,7 +15221,7 @@
         <v>-48.4375</v>
       </c>
       <c r="R164">
-        <v>-8.4839999999999999E-2</v>
+        <v>-8.4849999999999995E-2</v>
       </c>
       <c r="S164">
         <v>-48.4375</v>
@@ -15233,7 +15233,7 @@
         <v>-48.4375</v>
       </c>
       <c r="V164">
-        <v>-8.4909999999999999E-2</v>
+        <v>-8.4919999999999995E-2</v>
       </c>
       <c r="W164">
         <v>-48.4375</v>
@@ -15245,7 +15245,7 @@
         <v>-48.4375</v>
       </c>
       <c r="Z164">
-        <v>-8.4949999999999998E-2</v>
+        <v>-8.4959999999999994E-2</v>
       </c>
       <c r="AA164">
         <v>-48.4375</v>
@@ -15257,7 +15257,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AD164">
-        <v>-8.4930000000000005E-2</v>
+        <v>-8.4919999999999995E-2</v>
       </c>
     </row>
     <row r="165" spans="1:30" x14ac:dyDescent="0.25">
@@ -15313,7 +15313,7 @@
         <v>-50</v>
       </c>
       <c r="R165">
-        <v>-8.7599999999999997E-2</v>
+        <v>-8.7559999999999999E-2</v>
       </c>
       <c r="S165">
         <v>-50</v>
@@ -15325,7 +15325,7 @@
         <v>-50</v>
       </c>
       <c r="V165">
-        <v>-8.7639999999999996E-2</v>
+        <v>-8.7650000000000006E-2</v>
       </c>
       <c r="W165">
         <v>-50</v>
@@ -15349,7 +15349,7 @@
         <v>-50</v>
       </c>
       <c r="AD165">
-        <v>-8.7660000000000002E-2</v>
+        <v>-8.7599999999999997E-2</v>
       </c>
     </row>
     <row r="166" spans="1:30" x14ac:dyDescent="0.25">
@@ -15405,7 +15405,7 @@
         <v>-51.5625</v>
       </c>
       <c r="R166">
-        <v>-9.042E-2</v>
+        <v>-9.0429999999999996E-2</v>
       </c>
       <c r="S166">
         <v>-51.5625</v>
@@ -15417,7 +15417,7 @@
         <v>-51.5625</v>
       </c>
       <c r="V166">
-        <v>-9.0459999999999999E-2</v>
+        <v>-9.0450000000000003E-2</v>
       </c>
       <c r="W166">
         <v>-51.5625</v>
@@ -15429,7 +15429,7 @@
         <v>-51.5625</v>
       </c>
       <c r="Z166">
-        <v>-9.0509999999999993E-2</v>
+        <v>-9.0550000000000005E-2</v>
       </c>
       <c r="AA166">
         <v>-51.5625</v>
@@ -15497,7 +15497,7 @@
         <v>-53.125</v>
       </c>
       <c r="R167">
-        <v>-9.3160000000000007E-2</v>
+        <v>-9.3179999999999999E-2</v>
       </c>
       <c r="S167">
         <v>-53.125</v>
@@ -15509,19 +15509,19 @@
         <v>-53.125</v>
       </c>
       <c r="V167">
-        <v>-9.3200000000000005E-2</v>
+        <v>-9.3210000000000001E-2</v>
       </c>
       <c r="W167">
         <v>-53.125</v>
       </c>
       <c r="X167">
-        <v>-9.2530000000000001E-2</v>
+        <v>-9.2549999999999993E-2</v>
       </c>
       <c r="Y167">
         <v>-53.125</v>
       </c>
       <c r="Z167">
-        <v>-9.239E-2</v>
+        <v>-9.2369999999999994E-2</v>
       </c>
       <c r="AA167">
         <v>-53.125</v>
@@ -15589,7 +15589,7 @@
         <v>-54.6875</v>
       </c>
       <c r="R168">
-        <v>-9.5909999999999995E-2</v>
+        <v>-9.5920000000000005E-2</v>
       </c>
       <c r="S168">
         <v>-54.6875</v>
@@ -15601,19 +15601,19 @@
         <v>-54.6875</v>
       </c>
       <c r="V168">
-        <v>-9.5930000000000001E-2</v>
+        <v>-9.5949999999999994E-2</v>
       </c>
       <c r="W168">
         <v>-54.6875</v>
       </c>
       <c r="X168">
-        <v>-9.5909999999999995E-2</v>
+        <v>-9.5920000000000005E-2</v>
       </c>
       <c r="Y168">
         <v>-54.6875</v>
       </c>
       <c r="Z168">
-        <v>-9.5960000000000004E-2</v>
+        <v>-9.5979999999999996E-2</v>
       </c>
       <c r="AA168">
         <v>-54.6875</v>
@@ -15693,19 +15693,19 @@
         <v>-56.25</v>
       </c>
       <c r="V169">
-        <v>-9.8669999999999994E-2</v>
+        <v>-9.8650000000000002E-2</v>
       </c>
       <c r="W169">
         <v>-56.25</v>
       </c>
       <c r="X169">
-        <v>-9.8650000000000002E-2</v>
+        <v>-9.8669999999999994E-2</v>
       </c>
       <c r="Y169">
         <v>-56.25</v>
       </c>
       <c r="Z169">
-        <v>-9.8669999999999994E-2</v>
+        <v>-9.8659999999999998E-2</v>
       </c>
       <c r="AA169">
         <v>-56.25</v>
@@ -15767,7 +15767,7 @@
         <v>-57.8125</v>
       </c>
       <c r="P170">
-        <v>-0.10138</v>
+        <v>-0.1014</v>
       </c>
       <c r="Q170">
         <v>-57.8125</v>
@@ -15791,7 +15791,7 @@
         <v>-57.8125</v>
       </c>
       <c r="X170">
-        <v>-0.10138</v>
+        <v>-0.10141</v>
       </c>
       <c r="Y170">
         <v>-57.8125</v>
@@ -15841,7 +15841,7 @@
         <v>-59.375</v>
       </c>
       <c r="J171">
-        <v>-0.10414</v>
+        <v>-0.10419</v>
       </c>
       <c r="K171">
         <v>-59.375</v>
@@ -15865,13 +15865,13 @@
         <v>-59.375</v>
       </c>
       <c r="R171">
-        <v>-0.10412</v>
+        <v>-0.10414</v>
       </c>
       <c r="S171">
         <v>-59.375</v>
       </c>
       <c r="T171">
-        <v>-0.10414</v>
+        <v>-0.10417999999999999</v>
       </c>
       <c r="U171">
         <v>-59.375</v>
@@ -15883,13 +15883,13 @@
         <v>-59.375</v>
       </c>
       <c r="X171">
-        <v>-0.10414</v>
+        <v>-0.10412</v>
       </c>
       <c r="Y171">
         <v>-59.375</v>
       </c>
       <c r="Z171">
-        <v>-0.10416</v>
+        <v>-0.10421</v>
       </c>
       <c r="AA171">
         <v>-59.375</v>
@@ -15933,7 +15933,7 @@
         <v>-60.9375</v>
       </c>
       <c r="J172">
-        <v>-0.10688</v>
+        <v>-0.10682</v>
       </c>
       <c r="K172">
         <v>-60.9375</v>
@@ -15957,7 +15957,7 @@
         <v>-60.9375</v>
       </c>
       <c r="R172">
-        <v>-0.10687000000000001</v>
+        <v>-0.10688</v>
       </c>
       <c r="S172">
         <v>-60.9375</v>
@@ -15969,19 +15969,19 @@
         <v>-60.9375</v>
       </c>
       <c r="V172">
-        <v>-0.10689</v>
+        <v>-0.10692</v>
       </c>
       <c r="W172">
         <v>-60.9375</v>
       </c>
       <c r="X172">
-        <v>-0.10687000000000001</v>
+        <v>-0.10688</v>
       </c>
       <c r="Y172">
         <v>-60.9375</v>
       </c>
       <c r="Z172">
-        <v>-0.10689</v>
+        <v>-0.10688</v>
       </c>
       <c r="AA172">
         <v>-60.9375</v>
@@ -16049,7 +16049,7 @@
         <v>-62.5</v>
       </c>
       <c r="R173">
-        <v>-0.10961</v>
+        <v>-0.10962</v>
       </c>
       <c r="S173">
         <v>-62.5</v>
@@ -16061,19 +16061,19 @@
         <v>-62.5</v>
       </c>
       <c r="V173">
-        <v>-0.10963000000000001</v>
+        <v>-0.10965</v>
       </c>
       <c r="W173">
         <v>-62.5</v>
       </c>
       <c r="X173">
-        <v>-0.10961</v>
+        <v>-0.10962</v>
       </c>
       <c r="Y173">
         <v>-62.5</v>
       </c>
       <c r="Z173">
-        <v>-0.10965</v>
+        <v>-0.10964</v>
       </c>
       <c r="AA173">
         <v>-62.5</v>
@@ -16135,13 +16135,13 @@
         <v>-64.0625</v>
       </c>
       <c r="P174">
-        <v>-0.11236</v>
+        <v>-0.1124</v>
       </c>
       <c r="Q174">
         <v>-64.0625</v>
       </c>
       <c r="R174">
-        <v>-0.11236</v>
+        <v>-0.11235000000000001</v>
       </c>
       <c r="S174">
         <v>-64.0625</v>
@@ -16153,19 +16153,19 @@
         <v>-64.0625</v>
       </c>
       <c r="V174">
-        <v>-0.11236</v>
+        <v>-0.11233</v>
       </c>
       <c r="W174">
         <v>-64.0625</v>
       </c>
       <c r="X174">
-        <v>-0.11236</v>
+        <v>-0.11241</v>
       </c>
       <c r="Y174">
         <v>-64.0625</v>
       </c>
       <c r="Z174">
-        <v>-0.11241</v>
+        <v>-0.1124</v>
       </c>
       <c r="AA174">
         <v>-64.0625</v>
@@ -16185,7 +16185,7 @@
         <v>-65.625</v>
       </c>
       <c r="B175">
-        <v>-0.11486</v>
+        <v>-0.11466999999999999</v>
       </c>
       <c r="C175">
         <v>-65.625</v>
@@ -16227,13 +16227,13 @@
         <v>-65.625</v>
       </c>
       <c r="P175">
-        <v>-0.11512</v>
+        <v>-0.11511</v>
       </c>
       <c r="Q175">
         <v>-65.625</v>
       </c>
       <c r="R175">
-        <v>-0.11512</v>
+        <v>-0.11515</v>
       </c>
       <c r="S175">
         <v>-65.625</v>
@@ -16245,19 +16245,19 @@
         <v>-65.625</v>
       </c>
       <c r="V175">
-        <v>-0.11512</v>
+        <v>-0.11511</v>
       </c>
       <c r="W175">
         <v>-65.625</v>
       </c>
       <c r="X175">
-        <v>-0.11512</v>
+        <v>-0.11514000000000001</v>
       </c>
       <c r="Y175">
         <v>-65.625</v>
       </c>
       <c r="Z175">
-        <v>-0.11514000000000001</v>
+        <v>-0.1152</v>
       </c>
       <c r="AA175">
         <v>-65.625</v>
@@ -16277,7 +16277,7 @@
         <v>-67.1875</v>
       </c>
       <c r="B176">
-        <v>-0.11763999999999999</v>
+        <v>-0.11755</v>
       </c>
       <c r="C176">
         <v>-67.1875</v>
@@ -16319,13 +16319,13 @@
         <v>-67.1875</v>
       </c>
       <c r="P176">
-        <v>-0.11786000000000001</v>
+        <v>-0.11788</v>
       </c>
       <c r="Q176">
         <v>-67.1875</v>
       </c>
       <c r="R176">
-        <v>-0.11786000000000001</v>
+        <v>-0.11781999999999999</v>
       </c>
       <c r="S176">
         <v>-67.1875</v>
@@ -16343,13 +16343,13 @@
         <v>-67.1875</v>
       </c>
       <c r="X176">
-        <v>-0.11786000000000001</v>
+        <v>-0.11787</v>
       </c>
       <c r="Y176">
         <v>-67.1875</v>
       </c>
       <c r="Z176">
-        <v>-0.1179</v>
+        <v>-0.1181</v>
       </c>
       <c r="AA176">
         <v>-67.1875</v>
@@ -16369,7 +16369,7 @@
         <v>-68.75</v>
       </c>
       <c r="B177">
-        <v>-0.12037</v>
+        <v>-0.12007</v>
       </c>
       <c r="C177">
         <v>-68.75</v>
@@ -16417,7 +16417,7 @@
         <v>-68.75</v>
       </c>
       <c r="R177">
-        <v>-0.12060999999999999</v>
+        <v>-0.12062</v>
       </c>
       <c r="S177">
         <v>-68.75</v>
@@ -16435,7 +16435,7 @@
         <v>-68.75</v>
       </c>
       <c r="X177">
-        <v>-0.12060999999999999</v>
+        <v>-0.12062</v>
       </c>
       <c r="Y177">
         <v>-68.75</v>
@@ -16461,7 +16461,7 @@
         <v>-70.3125</v>
       </c>
       <c r="B178">
-        <v>-0.12309</v>
+        <v>-0.12331</v>
       </c>
       <c r="C178">
         <v>-70.3125</v>
@@ -16503,7 +16503,7 @@
         <v>-70.3125</v>
       </c>
       <c r="P178">
-        <v>-0.12335</v>
+        <v>-0.12334000000000001</v>
       </c>
       <c r="Q178">
         <v>-70.3125</v>
@@ -16527,13 +16527,13 @@
         <v>-70.3125</v>
       </c>
       <c r="X178">
-        <v>-0.12335</v>
+        <v>-0.12334000000000001</v>
       </c>
       <c r="Y178">
         <v>-70.3125</v>
       </c>
       <c r="Z178">
-        <v>-0.12339</v>
+        <v>-0.12343999999999999</v>
       </c>
       <c r="AA178">
         <v>-70.3125</v>
@@ -16553,7 +16553,7 @@
         <v>-71.875</v>
       </c>
       <c r="B179">
-        <v>-0.12581999999999999</v>
+        <v>-0.12583</v>
       </c>
       <c r="C179">
         <v>-71.875</v>
@@ -16619,13 +16619,13 @@
         <v>-71.875</v>
       </c>
       <c r="X179">
-        <v>-0.12608</v>
+        <v>-0.12605</v>
       </c>
       <c r="Y179">
         <v>-71.875</v>
       </c>
       <c r="Z179">
-        <v>-0.12612000000000001</v>
+        <v>-0.12614</v>
       </c>
       <c r="AA179">
         <v>-71.875</v>
@@ -16645,7 +16645,7 @@
         <v>-73.4375</v>
       </c>
       <c r="B180">
-        <v>-0.12859999999999999</v>
+        <v>-0.12887999999999999</v>
       </c>
       <c r="C180">
         <v>-73.4375</v>
@@ -16657,7 +16657,7 @@
         <v>-73.4375</v>
       </c>
       <c r="F180">
-        <v>-0.12878000000000001</v>
+        <v>-0.12878999999999999</v>
       </c>
       <c r="G180">
         <v>-73.4375</v>
@@ -16711,7 +16711,7 @@
         <v>-73.4375</v>
       </c>
       <c r="X180">
-        <v>-0.12884000000000001</v>
+        <v>-0.12887999999999999</v>
       </c>
       <c r="Y180">
         <v>-73.4375</v>
@@ -16737,7 +16737,7 @@
         <v>-75</v>
       </c>
       <c r="B181">
-        <v>-0.13131000000000001</v>
+        <v>-0.13164000000000001</v>
       </c>
       <c r="C181">
         <v>-75</v>
@@ -16803,13 +16803,13 @@
         <v>-75</v>
       </c>
       <c r="X181">
-        <v>-0.13156999999999999</v>
+        <v>-0.13155</v>
       </c>
       <c r="Y181">
         <v>-75</v>
       </c>
       <c r="Z181">
-        <v>-0.13161999999999999</v>
+        <v>-0.13170999999999999</v>
       </c>
       <c r="AA181">
         <v>-75</v>
@@ -16829,7 +16829,7 @@
         <v>-76.5625</v>
       </c>
       <c r="B182">
-        <v>-0.13406999999999999</v>
+        <v>-0.13435</v>
       </c>
       <c r="C182">
         <v>-76.5625</v>
@@ -16841,7 +16841,7 @@
         <v>-76.5625</v>
       </c>
       <c r="F182">
-        <v>-0.1343</v>
+        <v>-0.13428000000000001</v>
       </c>
       <c r="G182">
         <v>-76.5625</v>
@@ -16865,7 +16865,7 @@
         <v>-76.5625</v>
       </c>
       <c r="N182">
-        <v>-0.13435</v>
+        <v>-0.13436000000000001</v>
       </c>
       <c r="O182">
         <v>-76.5625</v>
@@ -16895,7 +16895,7 @@
         <v>-76.5625</v>
       </c>
       <c r="X182">
-        <v>-0.13431000000000001</v>
+        <v>-0.13431999999999999</v>
       </c>
       <c r="Y182">
         <v>-76.5625</v>
@@ -16921,13 +16921,13 @@
         <v>-78.125</v>
       </c>
       <c r="B183">
-        <v>-0.1368</v>
+        <v>-0.13711000000000001</v>
       </c>
       <c r="C183">
         <v>-78.125</v>
       </c>
       <c r="D183">
-        <v>-0.13708000000000001</v>
+        <v>-0.13711000000000001</v>
       </c>
       <c r="E183">
         <v>-78.125</v>
@@ -16993,7 +16993,7 @@
         <v>-78.125</v>
       </c>
       <c r="Z183">
-        <v>-0.13708000000000001</v>
+        <v>-0.13704</v>
       </c>
       <c r="AA183">
         <v>-78.125</v>
@@ -17013,7 +17013,7 @@
         <v>-79.6875</v>
       </c>
       <c r="B184">
-        <v>-0.13958000000000001</v>
+        <v>-0.13986000000000001</v>
       </c>
       <c r="C184">
         <v>-79.6875</v>
@@ -17025,7 +17025,7 @@
         <v>-79.6875</v>
       </c>
       <c r="F184">
-        <v>-0.13980999999999999</v>
+        <v>-0.13982</v>
       </c>
       <c r="G184">
         <v>-79.6875</v>
@@ -17079,13 +17079,13 @@
         <v>-79.6875</v>
       </c>
       <c r="X184">
-        <v>-0.13982</v>
+        <v>-0.13988</v>
       </c>
       <c r="Y184">
         <v>-79.6875</v>
       </c>
       <c r="Z184">
-        <v>-0.13986000000000001</v>
+        <v>-0.13988</v>
       </c>
       <c r="AA184">
         <v>-79.6875</v>
@@ -17105,7 +17105,7 @@
         <v>-81.25</v>
       </c>
       <c r="B185">
-        <v>-0.14232</v>
+        <v>-0.1426</v>
       </c>
       <c r="C185">
         <v>-81.25</v>
@@ -17117,7 +17117,7 @@
         <v>-81.25</v>
       </c>
       <c r="F185">
-        <v>-0.14219999999999999</v>
+        <v>-0.14230000000000001</v>
       </c>
       <c r="G185">
         <v>-81.25</v>
@@ -17159,7 +17159,7 @@
         <v>-81.25</v>
       </c>
       <c r="T185">
-        <v>-0.14262</v>
+        <v>-0.14263000000000001</v>
       </c>
       <c r="U185">
         <v>-81.25</v>
@@ -17171,13 +17171,13 @@
         <v>-81.25</v>
       </c>
       <c r="X185">
-        <v>-0.14255000000000001</v>
+        <v>-0.14257</v>
       </c>
       <c r="Y185">
         <v>-81.25</v>
       </c>
       <c r="Z185">
-        <v>-0.1426</v>
+        <v>-0.1431</v>
       </c>
       <c r="AA185">
         <v>-81.25</v>
@@ -17197,7 +17197,7 @@
         <v>-82.8125</v>
       </c>
       <c r="B186">
-        <v>-0.14507</v>
+        <v>-0.14535000000000001</v>
       </c>
       <c r="C186">
         <v>-82.8125</v>
@@ -17209,7 +17209,7 @@
         <v>-82.8125</v>
       </c>
       <c r="F186">
-        <v>-0.14538000000000001</v>
+        <v>-0.1454</v>
       </c>
       <c r="G186">
         <v>-82.8125</v>
@@ -17245,7 +17245,7 @@
         <v>-82.8125</v>
       </c>
       <c r="R186">
-        <v>-0.14538000000000001</v>
+        <v>-0.14535999999999999</v>
       </c>
       <c r="S186">
         <v>-82.8125</v>
@@ -17263,13 +17263,13 @@
         <v>-82.8125</v>
       </c>
       <c r="X186">
-        <v>-0.14530999999999999</v>
+        <v>-0.14529</v>
       </c>
       <c r="Y186">
         <v>-82.8125</v>
       </c>
       <c r="Z186">
-        <v>-0.14535000000000001</v>
+        <v>-0.14541000000000001</v>
       </c>
       <c r="AA186">
         <v>-82.8125</v>
@@ -17289,7 +17289,7 @@
         <v>-84.375</v>
       </c>
       <c r="B187">
-        <v>-0.14813000000000001</v>
+        <v>-0.14809</v>
       </c>
       <c r="C187">
         <v>-84.375</v>
@@ -17313,7 +17313,7 @@
         <v>-84.375</v>
       </c>
       <c r="J187">
-        <v>-0.14810999999999999</v>
+        <v>-0.14813000000000001</v>
       </c>
       <c r="K187">
         <v>-84.375</v>
@@ -17343,7 +17343,7 @@
         <v>-84.375</v>
       </c>
       <c r="T187">
-        <v>-0.14810999999999999</v>
+        <v>-0.14812</v>
       </c>
       <c r="U187">
         <v>-84.375</v>
@@ -17355,13 +17355,13 @@
         <v>-84.375</v>
       </c>
       <c r="X187">
-        <v>-0.14804999999999999</v>
+        <v>-0.14804</v>
       </c>
       <c r="Y187">
         <v>-84.375</v>
       </c>
       <c r="Z187">
-        <v>-0.14809</v>
+        <v>-0.14810999999999999</v>
       </c>
       <c r="AA187">
         <v>-84.375</v>
@@ -17381,7 +17381,7 @@
         <v>-85.9375</v>
       </c>
       <c r="B188">
-        <v>-0.15089</v>
+        <v>-0.15087</v>
       </c>
       <c r="C188">
         <v>-85.9375</v>
@@ -17393,7 +17393,7 @@
         <v>-85.9375</v>
       </c>
       <c r="F188">
-        <v>-0.15087</v>
+        <v>-0.15089</v>
       </c>
       <c r="G188">
         <v>-85.9375</v>
@@ -17447,13 +17447,13 @@
         <v>-85.9375</v>
       </c>
       <c r="X188">
-        <v>-0.15079999999999999</v>
+        <v>-0.15075</v>
       </c>
       <c r="Y188">
         <v>-85.9375</v>
       </c>
       <c r="Z188">
-        <v>-0.15085000000000001</v>
+        <v>-0.15090000000000001</v>
       </c>
       <c r="AA188">
         <v>-85.9375</v>
@@ -17473,7 +17473,7 @@
         <v>-87.5</v>
       </c>
       <c r="B189">
-        <v>-0.15367</v>
+        <v>-0.15359999999999999</v>
       </c>
       <c r="C189">
         <v>-87.5</v>
@@ -17485,7 +17485,7 @@
         <v>-87.5</v>
       </c>
       <c r="F189">
-        <v>-0.15362000000000001</v>
+        <v>-0.15361</v>
       </c>
       <c r="G189">
         <v>-87.5</v>
@@ -17527,7 +17527,7 @@
         <v>-87.5</v>
       </c>
       <c r="T189">
-        <v>-0.15362000000000001</v>
+        <v>-0.15359999999999999</v>
       </c>
       <c r="U189">
         <v>-87.5</v>
@@ -17539,13 +17539,13 @@
         <v>-87.5</v>
       </c>
       <c r="X189">
-        <v>-0.15356</v>
+        <v>-0.15354999999999999</v>
       </c>
       <c r="Y189">
         <v>-87.5</v>
       </c>
       <c r="Z189">
-        <v>-0.15357999999999999</v>
+        <v>-0.15361</v>
       </c>
       <c r="AA189">
         <v>-87.5</v>
@@ -17565,7 +17565,7 @@
         <v>-89.0625</v>
       </c>
       <c r="B190">
-        <v>-0.15642</v>
+        <v>-0.15636</v>
       </c>
       <c r="C190">
         <v>-89.0625</v>
@@ -17577,7 +17577,7 @@
         <v>-89.0625</v>
       </c>
       <c r="F190">
-        <v>-0.15637999999999999</v>
+        <v>-0.15640999999999999</v>
       </c>
       <c r="G190">
         <v>-89.0625</v>
@@ -17619,7 +17619,7 @@
         <v>-89.0625</v>
       </c>
       <c r="T190">
-        <v>-0.15637999999999999</v>
+        <v>-0.15640999999999999</v>
       </c>
       <c r="U190">
         <v>-89.0625</v>
@@ -17631,13 +17631,13 @@
         <v>-89.0625</v>
       </c>
       <c r="X190">
-        <v>-0.15631</v>
+        <v>-0.15631999999999999</v>
       </c>
       <c r="Y190">
         <v>-89.0625</v>
       </c>
       <c r="Z190">
-        <v>-0.15636</v>
+        <v>-0.15640999999999999</v>
       </c>
       <c r="AA190">
         <v>-89.0625</v>
@@ -17657,7 +17657,7 @@
         <v>-90.625</v>
       </c>
       <c r="B191">
-        <v>-0.15917999999999999</v>
+        <v>-0.15911</v>
       </c>
       <c r="C191">
         <v>-90.625</v>
@@ -17711,7 +17711,7 @@
         <v>-90.625</v>
       </c>
       <c r="T191">
-        <v>-0.15914</v>
+        <v>-0.15915000000000001</v>
       </c>
       <c r="U191">
         <v>-90.625</v>
@@ -17723,13 +17723,13 @@
         <v>-90.625</v>
       </c>
       <c r="X191">
-        <v>-0.15906999999999999</v>
+        <v>-0.15908</v>
       </c>
       <c r="Y191">
         <v>-90.625</v>
       </c>
       <c r="Z191">
-        <v>-0.15909000000000001</v>
+        <v>-0.15911</v>
       </c>
       <c r="AA191">
         <v>-90.625</v>
@@ -17749,7 +17749,7 @@
         <v>-92.1875</v>
       </c>
       <c r="B192">
-        <v>-0.16194</v>
+        <v>-0.16187000000000001</v>
       </c>
       <c r="C192">
         <v>-92.1875</v>
@@ -17761,7 +17761,7 @@
         <v>-92.1875</v>
       </c>
       <c r="F192">
-        <v>-0.16191</v>
+        <v>-0.16192999999999999</v>
       </c>
       <c r="G192">
         <v>-92.1875</v>
@@ -17815,13 +17815,13 @@
         <v>-92.1875</v>
       </c>
       <c r="X192">
-        <v>-0.16183</v>
+        <v>-0.16181999999999999</v>
       </c>
       <c r="Y192">
         <v>-92.1875</v>
       </c>
       <c r="Z192">
-        <v>-0.16187000000000001</v>
+        <v>-0.16188</v>
       </c>
       <c r="AA192">
         <v>-92.1875</v>
@@ -17841,7 +17841,7 @@
         <v>-93.75</v>
       </c>
       <c r="B193">
-        <v>-0.16469</v>
+        <v>-0.16463</v>
       </c>
       <c r="C193">
         <v>-93.75</v>
@@ -17907,13 +17907,13 @@
         <v>-93.75</v>
       </c>
       <c r="X193">
-        <v>-0.16456000000000001</v>
+        <v>-0.16455</v>
       </c>
       <c r="Y193">
         <v>-93.75</v>
       </c>
       <c r="Z193">
-        <v>-0.16461000000000001</v>
+        <v>-0.16461999999999999</v>
       </c>
       <c r="AA193">
         <v>-93.75</v>
@@ -17933,7 +17933,7 @@
         <v>-95.3125</v>
       </c>
       <c r="B194">
-        <v>-0.16744999999999999</v>
+        <v>-0.16736000000000001</v>
       </c>
       <c r="C194">
         <v>-95.3125</v>
@@ -17951,7 +17951,7 @@
         <v>-95.3125</v>
       </c>
       <c r="H194">
-        <v>-0.16739999999999999</v>
+        <v>-0.16736999999999999</v>
       </c>
       <c r="I194">
         <v>-95.3125</v>
@@ -17987,7 +17987,7 @@
         <v>-95.3125</v>
       </c>
       <c r="T194">
-        <v>-0.16738</v>
+        <v>-0.16741</v>
       </c>
       <c r="U194">
         <v>-95.3125</v>
@@ -17999,13 +17999,13 @@
         <v>-95.3125</v>
       </c>
       <c r="X194">
-        <v>-0.16732</v>
+        <v>-0.16736999999999999</v>
       </c>
       <c r="Y194">
         <v>-95.3125</v>
       </c>
       <c r="Z194">
-        <v>-0.16738</v>
+        <v>-0.16741</v>
       </c>
       <c r="AA194">
         <v>-95.3125</v>
@@ -18017,7 +18017,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AD194">
-        <v>-0.16739999999999999</v>
+        <v>-0.16750000000000001</v>
       </c>
     </row>
     <row r="195" spans="1:30" x14ac:dyDescent="0.25">
@@ -18025,7 +18025,7 @@
         <v>-96.875</v>
       </c>
       <c r="B195">
-        <v>-0.17018</v>
+        <v>-0.17011999999999999</v>
       </c>
       <c r="C195">
         <v>-96.875</v>
@@ -18079,7 +18079,7 @@
         <v>-96.875</v>
       </c>
       <c r="T195">
-        <v>-0.17016000000000001</v>
+        <v>-0.17015</v>
       </c>
       <c r="U195">
         <v>-96.875</v>
@@ -18091,7 +18091,7 @@
         <v>-96.875</v>
       </c>
       <c r="X195">
-        <v>-0.17005000000000001</v>
+        <v>-0.17008000000000001</v>
       </c>
       <c r="Y195">
         <v>-96.875</v>
@@ -18109,7 +18109,7 @@
         <v>-96.875</v>
       </c>
       <c r="AD195">
-        <v>-0.17016000000000001</v>
+        <v>-0.17018</v>
       </c>
     </row>
     <row r="196" spans="1:30" x14ac:dyDescent="0.25">
@@ -18117,7 +18117,7 @@
         <v>-98.4375</v>
       </c>
       <c r="B196">
-        <v>-0.17296</v>
+        <v>-0.1729</v>
       </c>
       <c r="C196">
         <v>-98.4375</v>
@@ -18147,7 +18147,7 @@
         <v>-98.4375</v>
       </c>
       <c r="L196">
-        <v>-0.17283000000000001</v>
+        <v>-0.17285</v>
       </c>
       <c r="M196">
         <v>-98.4375</v>
@@ -18189,7 +18189,7 @@
         <v>-98.4375</v>
       </c>
       <c r="Z196">
-        <v>-0.1729</v>
+        <v>-0.17349999999999999</v>
       </c>
       <c r="AA196">
         <v>-98.4375</v>
@@ -18201,7 +18201,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AD196">
-        <v>-0.17291999999999999</v>
+        <v>-0.17294999999999999</v>
       </c>
     </row>
     <row r="197" spans="1:30" x14ac:dyDescent="0.25">
@@ -18209,7 +18209,7 @@
         <v>-100</v>
       </c>
       <c r="B197">
-        <v>-0.17537</v>
+        <v>-0.17530999999999999</v>
       </c>
       <c r="C197">
         <v>-100</v>
@@ -18257,13 +18257,13 @@
         <v>-100</v>
       </c>
       <c r="R197">
-        <v>-0.17533000000000001</v>
+        <v>-0.17532</v>
       </c>
       <c r="S197">
         <v>-100</v>
       </c>
       <c r="T197">
-        <v>-0.17533000000000001</v>
+        <v>-0.17532</v>
       </c>
       <c r="U197">
         <v>-100</v>
@@ -18281,7 +18281,7 @@
         <v>-100</v>
       </c>
       <c r="Z197">
-        <v>-0.17530999999999999</v>
+        <v>-0.17532</v>
       </c>
       <c r="AA197">
         <v>-100</v>
@@ -18293,7 +18293,7 @@
         <v>-100</v>
       </c>
       <c r="AD197">
-        <v>-0.17535000000000001</v>
+        <v>-0.17535999999999999</v>
       </c>
     </row>
     <row r="198" spans="1:30" x14ac:dyDescent="0.25">
@@ -18301,19 +18301,19 @@
         <v>-98.4375</v>
       </c>
       <c r="B198">
-        <v>-0.17263999999999999</v>
+        <v>-0.17257</v>
       </c>
       <c r="C198">
         <v>-98.4375</v>
       </c>
       <c r="D198">
-        <v>-0.17258999999999999</v>
+        <v>-0.17261000000000001</v>
       </c>
       <c r="E198">
         <v>-98.4375</v>
       </c>
       <c r="F198">
-        <v>-0.17258999999999999</v>
+        <v>-0.17258000000000001</v>
       </c>
       <c r="G198">
         <v>-98.4375</v>
@@ -18355,7 +18355,7 @@
         <v>-98.4375</v>
       </c>
       <c r="T198">
-        <v>-0.17258999999999999</v>
+        <v>-0.17261000000000001</v>
       </c>
       <c r="U198">
         <v>-98.4375</v>
@@ -18367,13 +18367,13 @@
         <v>-98.4375</v>
       </c>
       <c r="X198">
-        <v>-0.17251</v>
+        <v>-0.17252000000000001</v>
       </c>
       <c r="Y198">
         <v>-98.4375</v>
       </c>
       <c r="Z198">
-        <v>-0.17257</v>
+        <v>-0.17258000000000001</v>
       </c>
       <c r="AA198">
         <v>-98.4375</v>
@@ -18393,7 +18393,7 @@
         <v>-96.875</v>
       </c>
       <c r="B199">
-        <v>-0.16986000000000001</v>
+        <v>-0.16979</v>
       </c>
       <c r="C199">
         <v>-96.875</v>
@@ -18441,13 +18441,13 @@
         <v>-96.875</v>
       </c>
       <c r="R199">
-        <v>-0.16982</v>
+        <v>-0.16983999999999999</v>
       </c>
       <c r="S199">
         <v>-96.875</v>
       </c>
       <c r="T199">
-        <v>-0.16982</v>
+        <v>-0.16980000000000001</v>
       </c>
       <c r="U199">
         <v>-96.875</v>
@@ -18459,13 +18459,13 @@
         <v>-96.875</v>
       </c>
       <c r="X199">
-        <v>-0.16972999999999999</v>
+        <v>-0.16975000000000001</v>
       </c>
       <c r="Y199">
         <v>-96.875</v>
       </c>
       <c r="Z199">
-        <v>-0.16979</v>
+        <v>-0.16977999999999999</v>
       </c>
       <c r="AA199">
         <v>-96.875</v>
@@ -18477,7 +18477,7 @@
         <v>-96.875</v>
       </c>
       <c r="AD199">
-        <v>-0.16983999999999999</v>
+        <v>-0.16988</v>
       </c>
     </row>
     <row r="200" spans="1:30" x14ac:dyDescent="0.25">
@@ -18485,7 +18485,7 @@
         <v>-95.3125</v>
       </c>
       <c r="B200">
-        <v>-0.16711999999999999</v>
+        <v>-0.16705999999999999</v>
       </c>
       <c r="C200">
         <v>-95.3125</v>
@@ -18509,7 +18509,7 @@
         <v>-95.3125</v>
       </c>
       <c r="J200">
-        <v>-0.16705999999999999</v>
+        <v>-0.16708999999999999</v>
       </c>
       <c r="K200">
         <v>-95.3125</v>
@@ -18521,7 +18521,7 @@
         <v>-95.3125</v>
       </c>
       <c r="N200">
-        <v>-0.16703999999999999</v>
+        <v>-0.16705</v>
       </c>
       <c r="O200">
         <v>-95.3125</v>
@@ -18533,13 +18533,13 @@
         <v>-95.3125</v>
       </c>
       <c r="R200">
-        <v>-0.16705999999999999</v>
+        <v>-0.16705</v>
       </c>
       <c r="S200">
         <v>-95.3125</v>
       </c>
       <c r="T200">
-        <v>-0.16705999999999999</v>
+        <v>-0.16705</v>
       </c>
       <c r="U200">
         <v>-95.3125</v>
@@ -18569,7 +18569,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AD200">
-        <v>-0.16708000000000001</v>
+        <v>-0.16707</v>
       </c>
     </row>
     <row r="201" spans="1:30" x14ac:dyDescent="0.25">
@@ -18577,7 +18577,7 @@
         <v>-93.75</v>
       </c>
       <c r="B201">
-        <v>-0.16435</v>
+        <v>-0.1643</v>
       </c>
       <c r="C201">
         <v>-93.75</v>
@@ -18601,7 +18601,7 @@
         <v>-93.75</v>
       </c>
       <c r="J201">
-        <v>-0.16433</v>
+        <v>-0.16431000000000001</v>
       </c>
       <c r="K201">
         <v>-93.75</v>
@@ -18625,13 +18625,13 @@
         <v>-93.75</v>
       </c>
       <c r="R201">
-        <v>-0.16433</v>
+        <v>-0.16431999999999999</v>
       </c>
       <c r="S201">
         <v>-93.75</v>
       </c>
       <c r="T201">
-        <v>-0.16433</v>
+        <v>-0.16431999999999999</v>
       </c>
       <c r="U201">
         <v>-93.75</v>
@@ -18643,7 +18643,7 @@
         <v>-93.75</v>
       </c>
       <c r="X201">
-        <v>-0.16424</v>
+        <v>-0.16425000000000001</v>
       </c>
       <c r="Y201">
         <v>-93.75</v>
@@ -18669,7 +18669,7 @@
         <v>-92.1875</v>
       </c>
       <c r="B202">
-        <v>-0.16161</v>
+        <v>-0.16155</v>
       </c>
       <c r="C202">
         <v>-92.1875</v>
@@ -18693,7 +18693,7 @@
         <v>-92.1875</v>
       </c>
       <c r="J202">
-        <v>-0.16156999999999999</v>
+        <v>-0.16158</v>
       </c>
       <c r="K202">
         <v>-92.1875</v>
@@ -18717,7 +18717,7 @@
         <v>-92.1875</v>
       </c>
       <c r="R202">
-        <v>-0.16156999999999999</v>
+        <v>-0.16155</v>
       </c>
       <c r="S202">
         <v>-92.1875</v>
@@ -18735,13 +18735,13 @@
         <v>-92.1875</v>
       </c>
       <c r="X202">
-        <v>-0.16148000000000001</v>
+        <v>-0.1615</v>
       </c>
       <c r="Y202">
         <v>-92.1875</v>
       </c>
       <c r="Z202">
-        <v>-0.16155</v>
+        <v>-0.16156000000000001</v>
       </c>
       <c r="AA202">
         <v>-92.1875</v>
@@ -18761,7 +18761,7 @@
         <v>-90.625</v>
       </c>
       <c r="B203">
-        <v>-0.15881000000000001</v>
+        <v>-0.15878999999999999</v>
       </c>
       <c r="C203">
         <v>-90.625</v>
@@ -18785,7 +18785,7 @@
         <v>-90.625</v>
       </c>
       <c r="J203">
-        <v>-0.15881000000000001</v>
+        <v>-0.15878999999999999</v>
       </c>
       <c r="K203">
         <v>-90.625</v>
@@ -18809,13 +18809,13 @@
         <v>-90.625</v>
       </c>
       <c r="R203">
-        <v>-0.15881000000000001</v>
+        <v>-0.15883</v>
       </c>
       <c r="S203">
         <v>-90.625</v>
       </c>
       <c r="T203">
-        <v>-0.15881000000000001</v>
+        <v>-0.15883</v>
       </c>
       <c r="U203">
         <v>-90.625</v>
@@ -18839,7 +18839,7 @@
         <v>-90.625</v>
       </c>
       <c r="AB203">
-        <v>-0.15883</v>
+        <v>-0.1588</v>
       </c>
       <c r="AC203">
         <v>-90.625</v>
@@ -18853,13 +18853,13 @@
         <v>-89.0625</v>
       </c>
       <c r="B204">
-        <v>-0.15609999999999999</v>
+        <v>-0.15603</v>
       </c>
       <c r="C204">
         <v>-89.0625</v>
       </c>
       <c r="D204">
-        <v>-0.15606</v>
+        <v>-0.15608</v>
       </c>
       <c r="E204">
         <v>-89.0625</v>
@@ -18901,7 +18901,7 @@
         <v>-89.0625</v>
       </c>
       <c r="R204">
-        <v>-0.15606</v>
+        <v>-0.15606999999999999</v>
       </c>
       <c r="S204">
         <v>-89.0625</v>
@@ -18919,19 +18919,19 @@
         <v>-89.0625</v>
       </c>
       <c r="X204">
-        <v>-0.15598999999999999</v>
+        <v>-0.15592</v>
       </c>
       <c r="Y204">
         <v>-89.0625</v>
       </c>
       <c r="Z204">
-        <v>-0.15603</v>
+        <v>-0.15611</v>
       </c>
       <c r="AA204">
         <v>-89.0625</v>
       </c>
       <c r="AB204">
-        <v>-0.15609999999999999</v>
+        <v>-0.15629999999999999</v>
       </c>
       <c r="AC204">
         <v>-89.0625</v>
@@ -18945,7 +18945,7 @@
         <v>-87.5</v>
       </c>
       <c r="B205">
-        <v>-0.15332000000000001</v>
+        <v>-0.15328</v>
       </c>
       <c r="C205">
         <v>-87.5</v>
@@ -18969,7 +18969,7 @@
         <v>-87.5</v>
       </c>
       <c r="J205">
-        <v>-0.15329999999999999</v>
+        <v>-0.153</v>
       </c>
       <c r="K205">
         <v>-87.5</v>
@@ -18999,7 +18999,7 @@
         <v>-87.5</v>
       </c>
       <c r="T205">
-        <v>-0.15329999999999999</v>
+        <v>-0.15331</v>
       </c>
       <c r="U205">
         <v>-87.5</v>
@@ -19011,19 +19011,19 @@
         <v>-87.5</v>
       </c>
       <c r="X205">
-        <v>-0.15321000000000001</v>
+        <v>-0.15322</v>
       </c>
       <c r="Y205">
         <v>-87.5</v>
       </c>
       <c r="Z205">
-        <v>-0.15326000000000001</v>
+        <v>-0.15328</v>
       </c>
       <c r="AA205">
         <v>-87.5</v>
       </c>
       <c r="AB205">
-        <v>-0.15332000000000001</v>
+        <v>-0.15331</v>
       </c>
       <c r="AC205">
         <v>-87.5</v>
@@ -19037,7 +19037,7 @@
         <v>-85.9375</v>
       </c>
       <c r="B206">
-        <v>-0.15059</v>
+        <v>-0.15051999999999999</v>
       </c>
       <c r="C206">
         <v>-85.9375</v>
@@ -19091,7 +19091,7 @@
         <v>-85.9375</v>
       </c>
       <c r="T206">
-        <v>-0.15054000000000001</v>
+        <v>-0.15056</v>
       </c>
       <c r="U206">
         <v>-85.9375</v>
@@ -19103,19 +19103,19 @@
         <v>-85.9375</v>
       </c>
       <c r="X206">
-        <v>-0.15048</v>
+        <v>-0.15045</v>
       </c>
       <c r="Y206">
         <v>-85.9375</v>
       </c>
       <c r="Z206">
-        <v>-0.15051999999999999</v>
+        <v>-0.15051</v>
       </c>
       <c r="AA206">
         <v>-85.9375</v>
       </c>
       <c r="AB206">
-        <v>-0.15057000000000001</v>
+        <v>-0.15057999999999999</v>
       </c>
       <c r="AC206">
         <v>-85.9375</v>
@@ -19129,7 +19129,7 @@
         <v>-84.375</v>
       </c>
       <c r="B207">
-        <v>-0.14781</v>
+        <v>-0.14777000000000001</v>
       </c>
       <c r="C207">
         <v>-84.375</v>
@@ -19195,19 +19195,19 @@
         <v>-84.375</v>
       </c>
       <c r="X207">
-        <v>-0.14771999999999999</v>
+        <v>-0.14774999999999999</v>
       </c>
       <c r="Y207">
         <v>-84.375</v>
       </c>
       <c r="Z207">
-        <v>-0.14777000000000001</v>
+        <v>-0.14776</v>
       </c>
       <c r="AA207">
         <v>-84.375</v>
       </c>
       <c r="AB207">
-        <v>-0.14781</v>
+        <v>-0.14782000000000001</v>
       </c>
       <c r="AC207">
         <v>-84.375</v>
@@ -19221,7 +19221,7 @@
         <v>-82.8125</v>
       </c>
       <c r="B208">
-        <v>-0.14507</v>
+        <v>-0.14502999999999999</v>
       </c>
       <c r="C208">
         <v>-82.8125</v>
@@ -19233,7 +19233,7 @@
         <v>-82.8125</v>
       </c>
       <c r="F208">
-        <v>-0.14507</v>
+        <v>-0.14507999999999999</v>
       </c>
       <c r="G208">
         <v>-82.8125</v>
@@ -19257,7 +19257,7 @@
         <v>-82.8125</v>
       </c>
       <c r="N208">
-        <v>-0.14501</v>
+        <v>-0.14502000000000001</v>
       </c>
       <c r="O208">
         <v>-82.8125</v>
@@ -19269,13 +19269,13 @@
         <v>-82.8125</v>
       </c>
       <c r="R208">
-        <v>-0.14505000000000001</v>
+        <v>-0.14502000000000001</v>
       </c>
       <c r="S208">
         <v>-82.8125</v>
       </c>
       <c r="T208">
-        <v>-0.14505000000000001</v>
+        <v>-0.14507999999999999</v>
       </c>
       <c r="U208">
         <v>-82.8125</v>
@@ -19313,7 +19313,7 @@
         <v>-81.25</v>
       </c>
       <c r="B209">
-        <v>-0.14232</v>
+        <v>-0.14227000000000001</v>
       </c>
       <c r="C209">
         <v>-81.25</v>
@@ -19349,7 +19349,7 @@
         <v>-81.25</v>
       </c>
       <c r="N209">
-        <v>-0.14224999999999999</v>
+        <v>-0.14226</v>
       </c>
       <c r="O209">
         <v>-81.25</v>
@@ -19379,7 +19379,7 @@
         <v>-81.25</v>
       </c>
       <c r="X209">
-        <v>-0.14223</v>
+        <v>-0.14224999999999999</v>
       </c>
       <c r="Y209">
         <v>-81.25</v>
@@ -19391,7 +19391,7 @@
         <v>-81.25</v>
       </c>
       <c r="AB209">
-        <v>-0.14233999999999999</v>
+        <v>-0.14235</v>
       </c>
       <c r="AC209">
         <v>-81.25</v>
@@ -19405,7 +19405,7 @@
         <v>-79.6875</v>
       </c>
       <c r="B210">
-        <v>-0.13958000000000001</v>
+        <v>-0.13952000000000001</v>
       </c>
       <c r="C210">
         <v>-79.6875</v>
@@ -19471,13 +19471,13 @@
         <v>-79.6875</v>
       </c>
       <c r="X210">
-        <v>-0.13947999999999999</v>
+        <v>-0.13944999999999999</v>
       </c>
       <c r="Y210">
         <v>-79.6875</v>
       </c>
       <c r="Z210">
-        <v>-0.13952000000000001</v>
+        <v>-0.13955000000000001</v>
       </c>
       <c r="AA210">
         <v>-79.6875</v>
@@ -19497,7 +19497,7 @@
         <v>-78.125</v>
       </c>
       <c r="B211">
-        <v>-0.1368</v>
+        <v>-0.13675999999999999</v>
       </c>
       <c r="C211">
         <v>-78.125</v>
@@ -19563,7 +19563,7 @@
         <v>-78.125</v>
       </c>
       <c r="X211">
-        <v>-0.13672000000000001</v>
+        <v>-0.13675000000000001</v>
       </c>
       <c r="Y211">
         <v>-78.125</v>
@@ -19575,7 +19575,7 @@
         <v>-78.125</v>
       </c>
       <c r="AB211">
-        <v>-0.13683000000000001</v>
+        <v>-0.13680999999999999</v>
       </c>
       <c r="AC211">
         <v>-78.125</v>
@@ -19589,7 +19589,7 @@
         <v>-76.5625</v>
       </c>
       <c r="B212">
-        <v>-0.13406999999999999</v>
+        <v>-0.13403000000000001</v>
       </c>
       <c r="C212">
         <v>-76.5625</v>
@@ -19643,7 +19643,7 @@
         <v>-76.5625</v>
       </c>
       <c r="T212">
-        <v>-0.13403000000000001</v>
+        <v>-0.13405</v>
       </c>
       <c r="U212">
         <v>-76.5625</v>
@@ -19655,7 +19655,7 @@
         <v>-76.5625</v>
       </c>
       <c r="X212">
-        <v>-0.13397999999999999</v>
+        <v>-0.13395000000000001</v>
       </c>
       <c r="Y212">
         <v>-76.5625</v>
@@ -19667,7 +19667,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AB212">
-        <v>-0.13406999999999999</v>
+        <v>-0.13408999999999999</v>
       </c>
       <c r="AC212">
         <v>-76.5625</v>
@@ -19681,7 +19681,7 @@
         <v>-75</v>
       </c>
       <c r="B213">
-        <v>-0.13131000000000001</v>
+        <v>-0.13127</v>
       </c>
       <c r="C213">
         <v>-75</v>
@@ -19735,7 +19735,7 @@
         <v>-75</v>
       </c>
       <c r="T213">
-        <v>-0.13128999999999999</v>
+        <v>-0.1313</v>
       </c>
       <c r="U213">
         <v>-75</v>
@@ -19753,13 +19753,13 @@
         <v>-75</v>
       </c>
       <c r="Z213">
-        <v>-0.13127</v>
+        <v>-0.13128000000000001</v>
       </c>
       <c r="AA213">
         <v>-75</v>
       </c>
       <c r="AB213">
-        <v>-0.13134000000000001</v>
+        <v>-0.13136999999999999</v>
       </c>
       <c r="AC213">
         <v>-75</v>
@@ -19773,7 +19773,7 @@
         <v>-73.4375</v>
       </c>
       <c r="B214">
-        <v>-0.12859999999999999</v>
+        <v>-0.12853999999999999</v>
       </c>
       <c r="C214">
         <v>-73.4375</v>
@@ -19809,7 +19809,7 @@
         <v>-73.4375</v>
       </c>
       <c r="N214">
-        <v>-0.12856000000000001</v>
+        <v>-0.12853999999999999</v>
       </c>
       <c r="O214">
         <v>-73.4375</v>
@@ -19839,7 +19839,7 @@
         <v>-73.4375</v>
       </c>
       <c r="X214">
-        <v>-0.12848999999999999</v>
+        <v>-0.12852</v>
       </c>
       <c r="Y214">
         <v>-73.4375</v>
@@ -19865,7 +19865,7 @@
         <v>-71.875</v>
       </c>
       <c r="B215">
-        <v>-0.12581999999999999</v>
+        <v>-0.12578</v>
       </c>
       <c r="C215">
         <v>-71.875</v>
@@ -19895,13 +19895,13 @@
         <v>-71.875</v>
       </c>
       <c r="L215">
-        <v>-0.12573999999999999</v>
+        <v>-0.12579000000000001</v>
       </c>
       <c r="M215">
         <v>-71.875</v>
       </c>
       <c r="N215">
-        <v>-0.1258</v>
+        <v>-0.12581999999999999</v>
       </c>
       <c r="O215">
         <v>-71.875</v>
@@ -19919,7 +19919,7 @@
         <v>-71.875</v>
       </c>
       <c r="T215">
-        <v>-0.1258</v>
+        <v>-0.12609999999999999</v>
       </c>
       <c r="U215">
         <v>-71.875</v>
@@ -19937,13 +19937,13 @@
         <v>-71.875</v>
       </c>
       <c r="Z215">
-        <v>-0.1258</v>
+        <v>-0.12578</v>
       </c>
       <c r="AA215">
         <v>-71.875</v>
       </c>
       <c r="AB215">
-        <v>-0.12584000000000001</v>
+        <v>-0.12586</v>
       </c>
       <c r="AC215">
         <v>-71.875</v>
@@ -19957,7 +19957,7 @@
         <v>-70.3125</v>
       </c>
       <c r="B216">
-        <v>-0.12309</v>
+        <v>-0.12304</v>
       </c>
       <c r="C216">
         <v>-70.3125</v>
@@ -19993,7 +19993,7 @@
         <v>-70.3125</v>
       </c>
       <c r="N216">
-        <v>-0.12304</v>
+        <v>-0.12306</v>
       </c>
       <c r="O216">
         <v>-70.3125</v>
@@ -20023,13 +20023,13 @@
         <v>-70.3125</v>
       </c>
       <c r="X216">
-        <v>-0.123</v>
+        <v>-0.1232</v>
       </c>
       <c r="Y216">
         <v>-70.3125</v>
       </c>
       <c r="Z216">
-        <v>-0.12304</v>
+        <v>-0.12307999999999999</v>
       </c>
       <c r="AA216">
         <v>-70.3125</v>
@@ -20049,7 +20049,7 @@
         <v>-68.75</v>
       </c>
       <c r="B217">
-        <v>-0.12037</v>
+        <v>-0.12028999999999999</v>
       </c>
       <c r="C217">
         <v>-68.75</v>
@@ -20085,7 +20085,7 @@
         <v>-68.75</v>
       </c>
       <c r="N217">
-        <v>-0.12031</v>
+        <v>-0.1203</v>
       </c>
       <c r="O217">
         <v>-68.75</v>
@@ -20121,13 +20121,13 @@
         <v>-68.75</v>
       </c>
       <c r="Z217">
-        <v>-0.12031</v>
+        <v>-0.12034</v>
       </c>
       <c r="AA217">
         <v>-68.75</v>
       </c>
       <c r="AB217">
-        <v>-0.12035</v>
+        <v>-0.12037</v>
       </c>
       <c r="AC217">
         <v>-68.75</v>
@@ -20141,7 +20141,7 @@
         <v>-67.1875</v>
       </c>
       <c r="B218">
-        <v>-0.11763999999999999</v>
+        <v>-0.11755</v>
       </c>
       <c r="C218">
         <v>-67.1875</v>
@@ -20177,7 +20177,7 @@
         <v>-67.1875</v>
       </c>
       <c r="N218">
-        <v>-0.11758</v>
+        <v>-0.1176</v>
       </c>
       <c r="O218">
         <v>-67.1875</v>
@@ -20207,19 +20207,19 @@
         <v>-67.1875</v>
       </c>
       <c r="X218">
-        <v>-0.11753</v>
+        <v>-0.11751</v>
       </c>
       <c r="Y218">
         <v>-67.1875</v>
       </c>
       <c r="Z218">
-        <v>-0.11758</v>
+        <v>-0.11752</v>
       </c>
       <c r="AA218">
         <v>-67.1875</v>
       </c>
       <c r="AB218">
-        <v>-0.11762</v>
+        <v>-0.11761000000000001</v>
       </c>
       <c r="AC218">
         <v>-67.1875</v>
@@ -20233,13 +20233,13 @@
         <v>-65.625</v>
       </c>
       <c r="B219">
-        <v>-0.11486</v>
+        <v>-0.1148</v>
       </c>
       <c r="C219">
         <v>-65.625</v>
       </c>
       <c r="D219">
-        <v>-0.11482000000000001</v>
+        <v>-0.11484</v>
       </c>
       <c r="E219">
         <v>-65.625</v>
@@ -20299,19 +20299,19 @@
         <v>-65.625</v>
       </c>
       <c r="X219">
-        <v>-0.11477999999999999</v>
+        <v>-0.11477</v>
       </c>
       <c r="Y219">
         <v>-65.625</v>
       </c>
       <c r="Z219">
-        <v>-0.11482000000000001</v>
+        <v>-0.1148</v>
       </c>
       <c r="AA219">
         <v>-65.625</v>
       </c>
       <c r="AB219">
-        <v>-0.11486</v>
+        <v>-0.11487</v>
       </c>
       <c r="AC219">
         <v>-65.625</v>
@@ -20325,7 +20325,7 @@
         <v>-64.0625</v>
       </c>
       <c r="B220">
-        <v>-0.11212999999999999</v>
+        <v>-0.11206000000000001</v>
       </c>
       <c r="C220">
         <v>-64.0625</v>
@@ -20391,19 +20391,19 @@
         <v>-64.0625</v>
       </c>
       <c r="X220">
-        <v>-0.11204</v>
+        <v>-0.11205</v>
       </c>
       <c r="Y220">
         <v>-64.0625</v>
       </c>
       <c r="Z220">
-        <v>-0.11208</v>
+        <v>-0.11211</v>
       </c>
       <c r="AA220">
         <v>-64.0625</v>
       </c>
       <c r="AB220">
-        <v>-0.11212999999999999</v>
+        <v>-0.11214</v>
       </c>
       <c r="AC220">
         <v>-64.0625</v>
@@ -20417,7 +20417,7 @@
         <v>-62.5</v>
       </c>
       <c r="B221">
-        <v>-0.10936999999999999</v>
+        <v>-0.10928</v>
       </c>
       <c r="C221">
         <v>-62.5</v>
@@ -20483,7 +20483,7 @@
         <v>-62.5</v>
       </c>
       <c r="X221">
-        <v>-0.10926</v>
+        <v>-0.10929999999999999</v>
       </c>
       <c r="Y221">
         <v>-62.5</v>
@@ -20495,7 +20495,7 @@
         <v>-62.5</v>
       </c>
       <c r="AB221">
-        <v>-0.10936999999999999</v>
+        <v>-0.10938000000000001</v>
       </c>
       <c r="AC221">
         <v>-62.5</v>
@@ -20509,7 +20509,7 @@
         <v>-60.9375</v>
       </c>
       <c r="B222">
-        <v>-0.10664</v>
+        <v>-0.10655000000000001</v>
       </c>
       <c r="C222">
         <v>-60.9375</v>
@@ -20575,13 +20575,13 @@
         <v>-60.9375</v>
       </c>
       <c r="X222">
-        <v>-0.10653</v>
+        <v>-0.10655000000000001</v>
       </c>
       <c r="Y222">
         <v>-60.9375</v>
       </c>
       <c r="Z222">
-        <v>-0.10657</v>
+        <v>-0.10657999999999999</v>
       </c>
       <c r="AA222">
         <v>-60.9375</v>
@@ -20601,7 +20601,7 @@
         <v>-59.375</v>
       </c>
       <c r="B223">
-        <v>-0.10385999999999999</v>
+        <v>-0.10378999999999999</v>
       </c>
       <c r="C223">
         <v>-59.375</v>
@@ -20655,7 +20655,7 @@
         <v>-59.375</v>
       </c>
       <c r="T223">
-        <v>-0.10382</v>
+        <v>-0.10384</v>
       </c>
       <c r="U223">
         <v>-59.375</v>
@@ -20667,19 +20667,19 @@
         <v>-59.375</v>
       </c>
       <c r="X223">
-        <v>-0.10378999999999999</v>
+        <v>-0.10381</v>
       </c>
       <c r="Y223">
         <v>-59.375</v>
       </c>
       <c r="Z223">
-        <v>-0.10384</v>
+        <v>-0.10388</v>
       </c>
       <c r="AA223">
         <v>-59.375</v>
       </c>
       <c r="AB223">
-        <v>-0.10388</v>
+        <v>-0.10387</v>
       </c>
       <c r="AC223">
         <v>-59.375</v>
@@ -20693,7 +20693,7 @@
         <v>-57.8125</v>
       </c>
       <c r="B224">
-        <v>-0.10112</v>
+        <v>-0.10106</v>
       </c>
       <c r="C224">
         <v>-57.8125</v>
@@ -20759,13 +20759,13 @@
         <v>-57.8125</v>
       </c>
       <c r="X224">
-        <v>-0.10106</v>
+        <v>-0.10105</v>
       </c>
       <c r="Y224">
         <v>-57.8125</v>
       </c>
       <c r="Z224">
-        <v>-0.10108</v>
+        <v>-0.10111000000000001</v>
       </c>
       <c r="AA224">
         <v>-57.8125</v>
@@ -20785,7 +20785,7 @@
         <v>-56.25</v>
       </c>
       <c r="B225">
-        <v>-9.8369999999999999E-2</v>
+        <v>-9.8320000000000005E-2</v>
       </c>
       <c r="C225">
         <v>-56.25</v>
@@ -20839,7 +20839,7 @@
         <v>-56.25</v>
       </c>
       <c r="T225">
-        <v>-9.8350000000000007E-2</v>
+        <v>-9.8400000000000001E-2</v>
       </c>
       <c r="U225">
         <v>-56.25</v>
@@ -20851,19 +20851,19 @@
         <v>-56.25</v>
       </c>
       <c r="X225">
-        <v>-9.8320000000000005E-2</v>
+        <v>-9.8330000000000001E-2</v>
       </c>
       <c r="Y225">
         <v>-56.25</v>
       </c>
       <c r="Z225">
-        <v>-9.8350000000000007E-2</v>
+        <v>-9.8409999999999997E-2</v>
       </c>
       <c r="AA225">
         <v>-56.25</v>
       </c>
       <c r="AB225">
-        <v>-9.8390000000000005E-2</v>
+        <v>-9.8339999999999997E-2</v>
       </c>
       <c r="AC225">
         <v>-56.25</v>
@@ -20877,7 +20877,7 @@
         <v>-54.6875</v>
       </c>
       <c r="B226">
-        <v>-9.5649999999999999E-2</v>
+        <v>-9.5570000000000002E-2</v>
       </c>
       <c r="C226">
         <v>-54.6875</v>
@@ -20943,13 +20943,13 @@
         <v>-54.6875</v>
       </c>
       <c r="X226">
-        <v>-9.5570000000000002E-2</v>
+        <v>-9.5579999999999998E-2</v>
       </c>
       <c r="Y226">
         <v>-54.6875</v>
       </c>
       <c r="Z226">
-        <v>-9.5630000000000007E-2</v>
+        <v>-9.5680000000000001E-2</v>
       </c>
       <c r="AA226">
         <v>-54.6875</v>
@@ -20969,7 +20969,7 @@
         <v>-53.125</v>
       </c>
       <c r="B227">
-        <v>-9.2899999999999996E-2</v>
+        <v>-9.2829999999999996E-2</v>
       </c>
       <c r="C227">
         <v>-53.125</v>
@@ -21035,7 +21035,7 @@
         <v>-53.125</v>
       </c>
       <c r="X227">
-        <v>-9.2829999999999996E-2</v>
+        <v>-9.2850000000000002E-2</v>
       </c>
       <c r="Y227">
         <v>-53.125</v>
@@ -21047,7 +21047,7 @@
         <v>-53.125</v>
       </c>
       <c r="AB227">
-        <v>-9.2899999999999996E-2</v>
+        <v>-9.2799999999999994E-2</v>
       </c>
       <c r="AC227">
         <v>-53.125</v>
@@ -21061,7 +21061,7 @@
         <v>-51.5625</v>
       </c>
       <c r="B228">
-        <v>-9.0160000000000004E-2</v>
+        <v>-9.01E-2</v>
       </c>
       <c r="C228">
         <v>-51.5625</v>
@@ -21127,7 +21127,7 @@
         <v>-51.5625</v>
       </c>
       <c r="X228">
-        <v>-9.01E-2</v>
+        <v>-9.0120000000000006E-2</v>
       </c>
       <c r="Y228">
         <v>-51.5625</v>
@@ -21153,7 +21153,7 @@
         <v>-50</v>
       </c>
       <c r="B229">
-        <v>-8.7319999999999995E-2</v>
+        <v>-8.7279999999999996E-2</v>
       </c>
       <c r="C229">
         <v>-50</v>
@@ -21219,13 +21219,13 @@
         <v>-50</v>
       </c>
       <c r="X229">
-        <v>-8.7279999999999996E-2</v>
+        <v>-8.727E-2</v>
       </c>
       <c r="Y229">
         <v>-50</v>
       </c>
       <c r="Z229">
-        <v>-8.7319999999999995E-2</v>
+        <v>-8.7379999999999999E-2</v>
       </c>
       <c r="AA229">
         <v>-50</v>
@@ -21245,7 +21245,7 @@
         <v>-48.4375</v>
       </c>
       <c r="B230">
-        <v>-8.4589999999999999E-2</v>
+        <v>-8.4540000000000004E-2</v>
       </c>
       <c r="C230">
         <v>-48.4375</v>
@@ -21311,13 +21311,13 @@
         <v>-48.4375</v>
       </c>
       <c r="X230">
-        <v>-8.4540000000000004E-2</v>
+        <v>-8.455E-2</v>
       </c>
       <c r="Y230">
         <v>-48.4375</v>
       </c>
       <c r="Z230">
-        <v>-8.4589999999999999E-2</v>
+        <v>-8.4610000000000005E-2</v>
       </c>
       <c r="AA230">
         <v>-48.4375</v>
@@ -21337,7 +21337,7 @@
         <v>-46.875</v>
       </c>
       <c r="B231">
-        <v>-8.183E-2</v>
+        <v>-8.1790000000000002E-2</v>
       </c>
       <c r="C231">
         <v>-46.875</v>
@@ -21403,13 +21403,13 @@
         <v>-46.875</v>
       </c>
       <c r="X231">
-        <v>-8.1809999999999994E-2</v>
+        <v>-8.1869999999999998E-2</v>
       </c>
       <c r="Y231">
         <v>-46.875</v>
       </c>
       <c r="Z231">
-        <v>-8.183E-2</v>
+        <v>-8.1879999999999994E-2</v>
       </c>
       <c r="AA231">
         <v>-46.875</v>
@@ -21429,7 +21429,7 @@
         <v>-45.3125</v>
       </c>
       <c r="B232">
-        <v>-7.9089999999999994E-2</v>
+        <v>-7.9049999999999995E-2</v>
       </c>
       <c r="C232">
         <v>-45.3125</v>
@@ -21495,13 +21495,13 @@
         <v>-45.3125</v>
       </c>
       <c r="X232">
-        <v>-7.9070000000000001E-2</v>
+        <v>-7.9079999999999998E-2</v>
       </c>
       <c r="Y232">
         <v>-45.3125</v>
       </c>
       <c r="Z232">
-        <v>-7.9089999999999994E-2</v>
+        <v>-7.9070000000000001E-2</v>
       </c>
       <c r="AA232">
         <v>-45.3125</v>
@@ -21521,7 +21521,7 @@
         <v>-43.75</v>
       </c>
       <c r="B233">
-        <v>-7.6319999999999999E-2</v>
+        <v>-7.6289999999999997E-2</v>
       </c>
       <c r="C233">
         <v>-43.75</v>
@@ -21587,13 +21587,13 @@
         <v>-43.75</v>
       </c>
       <c r="X233">
-        <v>-7.6319999999999999E-2</v>
+        <v>-7.6350000000000001E-2</v>
       </c>
       <c r="Y233">
         <v>-43.75</v>
       </c>
       <c r="Z233">
-        <v>-7.6359999999999997E-2</v>
+        <v>-7.6350000000000001E-2</v>
       </c>
       <c r="AA233">
         <v>-43.75</v>
@@ -21613,7 +21613,7 @@
         <v>-42.1875</v>
       </c>
       <c r="B234">
-        <v>-7.3539999999999994E-2</v>
+        <v>-7.356E-2</v>
       </c>
       <c r="C234">
         <v>-42.1875</v>
@@ -21679,13 +21679,13 @@
         <v>-42.1875</v>
       </c>
       <c r="X234">
-        <v>-7.3599999999999999E-2</v>
+        <v>-7.3590000000000003E-2</v>
       </c>
       <c r="Y234">
         <v>-42.1875</v>
       </c>
       <c r="Z234">
-        <v>-7.3620000000000005E-2</v>
+        <v>-7.3649999999999993E-2</v>
       </c>
       <c r="AA234">
         <v>-42.1875</v>
@@ -21705,7 +21705,7 @@
         <v>-40.625</v>
       </c>
       <c r="B235">
-        <v>-7.102E-2</v>
+        <v>-7.0830000000000004E-2</v>
       </c>
       <c r="C235">
         <v>-40.625</v>
@@ -21771,13 +21771,13 @@
         <v>-40.625</v>
       </c>
       <c r="X235">
-        <v>-7.0830000000000004E-2</v>
+        <v>-7.0809999999999998E-2</v>
       </c>
       <c r="Y235">
         <v>-40.625</v>
       </c>
       <c r="Z235">
-        <v>-7.0870000000000002E-2</v>
+        <v>-7.0879999999999999E-2</v>
       </c>
       <c r="AA235">
         <v>-40.625</v>
@@ -21797,7 +21797,7 @@
         <v>-39.0625</v>
       </c>
       <c r="B236">
-        <v>-6.8839999999999998E-2</v>
+        <v>-6.8049999999999999E-2</v>
       </c>
       <c r="C236">
         <v>-39.0625</v>
@@ -21889,7 +21889,7 @@
         <v>-37.5</v>
       </c>
       <c r="B237">
-        <v>-6.6400000000000001E-2</v>
+        <v>-6.497E-2</v>
       </c>
       <c r="C237">
         <v>-37.5</v>
@@ -21955,13 +21955,13 @@
         <v>-37.5</v>
       </c>
       <c r="X237">
-        <v>-6.5329999999999999E-2</v>
+        <v>-6.5320000000000003E-2</v>
       </c>
       <c r="Y237">
         <v>-37.5</v>
       </c>
       <c r="Z237">
-        <v>-6.54E-2</v>
+        <v>-6.5350000000000005E-2</v>
       </c>
       <c r="AA237">
         <v>-37.5</v>
@@ -21981,7 +21981,7 @@
         <v>-35.9375</v>
       </c>
       <c r="B238">
-        <v>-6.4219999999999999E-2</v>
+        <v>-5.9540000000000003E-2</v>
       </c>
       <c r="C238">
         <v>-35.9375</v>
@@ -21993,7 +21993,7 @@
         <v>-35.9375</v>
       </c>
       <c r="F238">
-        <v>-6.198E-2</v>
+        <v>-6.1960000000000001E-2</v>
       </c>
       <c r="G238">
         <v>-35.9375</v>
@@ -22005,7 +22005,7 @@
         <v>-35.9375</v>
       </c>
       <c r="J238">
-        <v>-6.1719999999999997E-2</v>
+        <v>-6.1740000000000003E-2</v>
       </c>
       <c r="K238">
         <v>-35.9375</v>
@@ -22053,7 +22053,7 @@
         <v>-35.9375</v>
       </c>
       <c r="Z238">
-        <v>-6.2640000000000001E-2</v>
+        <v>-6.2649999999999997E-2</v>
       </c>
       <c r="AA238">
         <v>-35.9375</v>
@@ -22073,7 +22073,7 @@
         <v>-34.375</v>
       </c>
       <c r="B239">
-        <v>-6.1780000000000002E-2</v>
+        <v>-1.094E-2</v>
       </c>
       <c r="C239">
         <v>-34.375</v>
@@ -22085,7 +22085,7 @@
         <v>-34.375</v>
       </c>
       <c r="F239">
-        <v>-5.8220000000000001E-2</v>
+        <v>-5.8229999999999997E-2</v>
       </c>
       <c r="G239">
         <v>-34.375</v>
@@ -22097,7 +22097,7 @@
         <v>-34.375</v>
       </c>
       <c r="J239">
-        <v>-5.824E-2</v>
+        <v>-5.8220000000000001E-2</v>
       </c>
       <c r="K239">
         <v>-34.375</v>
@@ -22139,7 +22139,7 @@
         <v>-34.375</v>
       </c>
       <c r="X239">
-        <v>-5.9859999999999997E-2</v>
+        <v>-5.9819999999999998E-2</v>
       </c>
       <c r="Y239">
         <v>-34.375</v>
@@ -22165,7 +22165,7 @@
         <v>-32.8125</v>
       </c>
       <c r="B240">
-        <v>-5.9330000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C240">
         <v>-32.8125</v>
@@ -22177,7 +22177,7 @@
         <v>-32.8125</v>
       </c>
       <c r="F240">
-        <v>-5.5410000000000001E-2</v>
+        <v>-5.5399999999999998E-2</v>
       </c>
       <c r="G240">
         <v>-32.8125</v>
@@ -22189,13 +22189,13 @@
         <v>-32.8125</v>
       </c>
       <c r="J240">
-        <v>-5.4760000000000003E-2</v>
+        <v>-5.4780000000000002E-2</v>
       </c>
       <c r="K240">
         <v>-32.8125</v>
       </c>
       <c r="L240">
-        <v>-5.7149999999999999E-2</v>
+        <v>-5.7119999999999997E-2</v>
       </c>
       <c r="M240">
         <v>-32.8125</v>
@@ -22237,7 +22237,7 @@
         <v>-32.8125</v>
       </c>
       <c r="Z240">
-        <v>-5.7149999999999999E-2</v>
+        <v>-5.7160000000000002E-2</v>
       </c>
       <c r="AA240">
         <v>-32.8125</v>
@@ -22257,7 +22257,7 @@
         <v>-31.25</v>
       </c>
       <c r="B241">
-        <v>-5.7160000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C241">
         <v>-31.25</v>
@@ -22269,7 +22269,7 @@
         <v>-31.25</v>
       </c>
       <c r="F241">
-        <v>-5.2589999999999998E-2</v>
+        <v>-5.2609999999999997E-2</v>
       </c>
       <c r="G241">
         <v>-31.25</v>
@@ -22281,7 +22281,7 @@
         <v>-31.25</v>
       </c>
       <c r="J241">
-        <v>-5.2159999999999998E-2</v>
+        <v>-5.2179999999999997E-2</v>
       </c>
       <c r="K241">
         <v>-31.25</v>
@@ -22323,13 +22323,13 @@
         <v>-31.25</v>
       </c>
       <c r="X241">
-        <v>-5.4370000000000002E-2</v>
+        <v>-5.4330000000000003E-2</v>
       </c>
       <c r="Y241">
         <v>-31.25</v>
       </c>
       <c r="Z241">
-        <v>-5.4420000000000003E-2</v>
+        <v>-5.4480000000000001E-2</v>
       </c>
       <c r="AA241">
         <v>-31.25</v>
@@ -22349,7 +22349,7 @@
         <v>-29.6875</v>
       </c>
       <c r="B242">
-        <v>-5.4989999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C242">
         <v>-29.6875</v>
@@ -22367,7 +22367,7 @@
         <v>-29.6875</v>
       </c>
       <c r="H242">
-        <v>-4.8680000000000001E-2</v>
+        <v>-4.8669999999999998E-2</v>
       </c>
       <c r="I242">
         <v>-29.6875</v>
@@ -22415,7 +22415,7 @@
         <v>-29.6875</v>
       </c>
       <c r="X242">
-        <v>-5.16E-2</v>
+        <v>-5.1200000000000002E-2</v>
       </c>
       <c r="Y242">
         <v>-29.6875</v>
@@ -22441,7 +22441,7 @@
         <v>-28.125</v>
       </c>
       <c r="B243">
-        <v>-5.3089999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="C243">
         <v>-28.125</v>
@@ -22453,7 +22453,7 @@
         <v>-28.125</v>
       </c>
       <c r="F243">
-        <v>-4.6010000000000002E-2</v>
+        <v>-4.6019999999999998E-2</v>
       </c>
       <c r="G243">
         <v>-28.125</v>
@@ -22465,7 +22465,7 @@
         <v>-28.125</v>
       </c>
       <c r="J243">
-        <v>-4.5199999999999997E-2</v>
+        <v>-4.5190000000000001E-2</v>
       </c>
       <c r="K243">
         <v>-28.125</v>
@@ -22507,13 +22507,13 @@
         <v>-28.125</v>
       </c>
       <c r="X243">
-        <v>-4.8410000000000002E-2</v>
+        <v>-4.8419999999999998E-2</v>
       </c>
       <c r="Y243">
         <v>-28.125</v>
       </c>
       <c r="Z243">
-        <v>-4.845E-2</v>
+        <v>-4.8460000000000003E-2</v>
       </c>
       <c r="AA243">
         <v>-28.125</v>
@@ -22533,7 +22533,7 @@
         <v>-26.5625</v>
       </c>
       <c r="B244">
-        <v>-5.0909999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C244">
         <v>-26.5625</v>
@@ -22545,7 +22545,7 @@
         <v>-26.5625</v>
       </c>
       <c r="F244">
-        <v>-4.3189999999999999E-2</v>
+        <v>-4.3209999999999998E-2</v>
       </c>
       <c r="G244">
         <v>-26.5625</v>
@@ -22557,7 +22557,7 @@
         <v>-26.5625</v>
       </c>
       <c r="J244">
-        <v>-4.2590000000000003E-2</v>
+        <v>-4.2619999999999998E-2</v>
       </c>
       <c r="K244">
         <v>-26.5625</v>
@@ -22599,13 +22599,13 @@
         <v>-26.5625</v>
       </c>
       <c r="X244">
-        <v>-4.3819999999999998E-2</v>
+        <v>-4.3880000000000002E-2</v>
       </c>
       <c r="Y244">
         <v>-26.5625</v>
       </c>
       <c r="Z244">
-        <v>-4.3839999999999997E-2</v>
+        <v>-4.385E-2</v>
       </c>
       <c r="AA244">
         <v>-26.5625</v>
@@ -22625,7 +22625,7 @@
         <v>-25</v>
       </c>
       <c r="B245">
-        <v>-4.9009999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="C245">
         <v>-25</v>
@@ -22691,7 +22691,7 @@
         <v>-25</v>
       </c>
       <c r="X245">
-        <v>-4.011E-2</v>
+        <v>-4.0120000000000003E-2</v>
       </c>
       <c r="Y245">
         <v>-25</v>
@@ -22729,7 +22729,7 @@
         <v>-23.4375</v>
       </c>
       <c r="F246">
-        <v>-3.567E-2</v>
+        <v>-3.5650000000000001E-2</v>
       </c>
       <c r="G246">
         <v>-23.4375</v>
@@ -22741,7 +22741,7 @@
         <v>-23.4375</v>
       </c>
       <c r="J246">
-        <v>-3.6510000000000001E-2</v>
+        <v>-3.653E-2</v>
       </c>
       <c r="K246">
         <v>-23.4375</v>
@@ -22833,7 +22833,7 @@
         <v>-21.875</v>
       </c>
       <c r="J247">
-        <v>-3.3029999999999997E-2</v>
+        <v>-3.3079999999999998E-2</v>
       </c>
       <c r="K247">
         <v>-21.875</v>
